--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H252"/>
+  <dimension ref="A1:H255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H6">
-        <v>62</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -1049,23 +1049,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -1081,23 +1081,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D23">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="E23">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>211</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1108,28 +1108,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D24">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H24">
-        <v>75</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25">
@@ -1145,23 +1145,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H25">
-        <v>6</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G26">
         <v>1</v>
       </c>
       <c r="H26">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27">
@@ -1209,23 +1209,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D27">
-        <v>186</v>
+        <v>8</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="G27">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>148</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D28">
-        <v>36</v>
+        <v>186</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F28">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H28">
-        <v>36</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D29">
-        <v>353</v>
+        <v>36</v>
       </c>
       <c r="E29">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>353</v>
+        <v>36</v>
       </c>
       <c r="G29">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>353</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D30">
-        <v>50</v>
+        <v>395</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="F30">
-        <v>50</v>
+        <v>395</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H30">
-        <v>50</v>
+        <v>395</v>
       </c>
     </row>
     <row r="31">
@@ -1337,20 +1337,20 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D31">
         <v>50</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31">
         <v>50</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>50</v>
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D32">
-        <v>426</v>
+        <v>123</v>
       </c>
       <c r="E32">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>426</v>
+        <v>123</v>
       </c>
       <c r="G32">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="H32">
-        <v>426</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33">
@@ -1396,28 +1396,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D33">
-        <v>16</v>
+        <v>412</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="F33">
-        <v>16</v>
+        <v>412</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H33">
-        <v>16</v>
+        <v>412</v>
       </c>
     </row>
     <row r="34">
@@ -1433,23 +1433,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35">
@@ -1465,11 +1465,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D35">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1478,10 +1478,10 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D36">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -1529,23 +1529,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D37">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -1556,28 +1556,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1593,23 +1593,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D39">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="G39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
@@ -1620,28 +1620,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>107</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41">
@@ -1657,11 +1657,11 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1670,10 +1670,10 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1689,11 +1689,11 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D42">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1702,30 +1702,30 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D43">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -1753,11 +1753,11 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1780,16 +1780,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D45">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1817,11 +1817,11 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1849,7 +1849,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D47">
@@ -1881,11 +1881,11 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1945,11 +1945,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D50">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1977,11 +1977,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D52">
@@ -2041,11 +2041,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2073,11 +2073,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D54">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2105,11 +2105,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2137,11 +2137,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D56">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2201,11 +2201,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2233,11 +2233,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2265,11 +2265,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2292,16 +2292,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2329,11 +2329,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D62">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2361,11 +2361,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D63">
-        <v>772</v>
+        <v>12</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>88</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2425,11 +2425,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D65">
-        <v>175</v>
+        <v>2</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2457,11 +2457,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D67">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2521,11 +2521,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D68">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2585,11 +2585,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D70">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2617,11 +2617,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D71">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D72">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D73">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D74">
-        <v>245</v>
+        <v>83</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D75">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2777,11 +2777,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>245</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2809,11 +2809,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D77">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D78">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D79">
-        <v>715</v>
+        <v>56</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D80">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2937,11 +2937,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D81">
-        <v>84</v>
+        <v>715</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D82">
@@ -2996,16 +2996,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D83">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3028,16 +3028,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D84">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3065,11 +3065,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D85">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D86">
-        <v>180</v>
+        <v>26</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D87">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3161,11 +3161,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D88">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D89">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3225,11 +3225,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D90">
-        <v>41</v>
+        <v>154</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D91">
-        <v>180</v>
+        <v>47</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D92">
-        <v>36</v>
+        <v>257</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D93">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3353,11 +3353,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D94">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D95">
-        <v>241</v>
+        <v>12</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D96">
-        <v>236</v>
+        <v>38</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3449,11 +3449,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D97">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D98">
-        <v>9</v>
+        <v>236</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3513,11 +3513,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D99">
-        <v>180</v>
+        <v>61</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D100">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D101">
-        <v>216</v>
+        <v>164</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D102">
-        <v>144</v>
+        <v>22</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3636,16 +3636,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3668,16 +3668,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D104">
-        <v>3</v>
+        <v>192</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3700,16 +3700,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3796,16 +3796,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D108">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3828,16 +3828,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D109">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3860,16 +3860,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D110">
-        <v>595</v>
+        <v>2</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D111">
-        <v>432</v>
+        <v>99</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D112">
-        <v>102</v>
+        <v>40</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D113">
-        <v>72</v>
+        <v>595</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D114">
-        <v>72</v>
+        <v>426</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4025,11 +4025,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D115">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4057,11 +4057,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D116">
-        <v>613</v>
+        <v>72</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4089,11 +4089,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D117">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4121,11 +4121,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D118">
-        <v>22</v>
+        <v>613</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4153,11 +4153,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D119">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4185,11 +4185,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D120">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4217,11 +4217,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D121">
-        <v>687</v>
+        <v>122</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4249,11 +4249,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D122">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D123">
-        <v>718</v>
+        <v>687</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D124">
-        <v>530</v>
+        <v>16</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4345,11 +4345,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D125">
-        <v>254</v>
+        <v>718</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4377,11 +4377,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D126">
-        <v>168</v>
+        <v>530</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4404,16 +4404,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D127">
-        <v>7</v>
+        <v>218</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4436,16 +4436,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>168</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D129">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4505,11 +4505,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D130">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D131">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4569,11 +4569,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4601,11 +4601,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D133">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4633,11 +4633,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D134">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4665,11 +4665,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D135">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4697,11 +4697,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4729,11 +4729,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D137">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4761,11 +4761,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D138">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4793,11 +4793,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D139">
-        <v>1657</v>
+        <v>11</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4815,21 +4815,21 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D140">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4847,21 +4847,21 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D141">
-        <v>3434</v>
+        <v>1657</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="D142">
-        <v>8603</v>
+        <v>54</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="D143">
-        <v>5</v>
+        <v>3360</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4957,7 +4957,7 @@
         </is>
       </c>
       <c r="D144">
-        <v>9900</v>
+        <v>8023</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="D145">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5007,21 +5007,21 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>9900</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5039,21 +5039,21 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="D148">
-        <v>3816</v>
+        <v>1</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="D149">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5135,21 +5135,21 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D150">
-        <v>46</v>
+        <v>2916</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5167,21 +5167,21 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D151">
-        <v>72</v>
+        <v>3816</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5199,21 +5199,21 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D152">
-        <v>9216</v>
+        <v>8</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5236,7 +5236,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="D153">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="D154">
-        <v>8100</v>
+        <v>72</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="D155">
-        <v>14</v>
+        <v>8964</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5327,21 +5327,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D156">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5359,21 +5359,21 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D157">
-        <v>8</v>
+        <v>8100</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5391,21 +5391,21 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D158">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D159">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5465,11 +5465,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D160">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D161">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5524,16 +5524,16 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D162">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5556,16 +5556,16 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5588,16 +5588,16 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D164">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5625,11 +5625,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D165">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5657,11 +5657,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D166">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D167">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5721,11 +5721,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D168">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5753,11 +5753,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D169">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5785,11 +5785,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D170">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5817,11 +5817,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D171">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5849,11 +5849,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D172">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5881,11 +5881,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D173">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5913,11 +5913,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D174">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5945,11 +5945,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D175">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5977,11 +5977,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D176">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -6009,11 +6009,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6041,11 +6041,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6073,11 +6073,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D179">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6100,16 +6100,16 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D180">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6132,16 +6132,16 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D181">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6164,16 +6164,16 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D182">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6201,11 +6201,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D183">
-        <v>304</v>
+        <v>115</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6233,11 +6233,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D184">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6265,11 +6265,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D185">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6297,11 +6297,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D186">
-        <v>81</v>
+        <v>304</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6329,11 +6329,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D187">
-        <v>248</v>
+        <v>30</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6361,11 +6361,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D188">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6393,11 +6393,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D189">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6425,11 +6425,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D190">
-        <v>12</v>
+        <v>248</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6457,11 +6457,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D191">
-        <v>222</v>
+        <v>89</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6489,11 +6489,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6521,11 +6521,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D193">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6553,11 +6553,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D194">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6585,11 +6585,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D195">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6617,11 +6617,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D196">
-        <v>232</v>
+        <v>8</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6649,11 +6649,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D197">
-        <v>28</v>
+        <v>182</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D198">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6713,11 +6713,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D199">
-        <v>30</v>
+        <v>204</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6745,11 +6745,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D200">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6777,11 +6777,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D201">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6809,11 +6809,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D202">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6841,11 +6841,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D203">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6873,11 +6873,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D204">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6900,16 +6900,16 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D205">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6932,16 +6932,16 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D206">
-        <v>295</v>
+        <v>121</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6964,16 +6964,16 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D207">
-        <v>420</v>
+        <v>114</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -7001,11 +7001,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D208">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7033,11 +7033,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D209">
-        <v>146</v>
+        <v>295</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7065,11 +7065,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D210">
-        <v>170</v>
+        <v>420</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7097,11 +7097,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D211">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D212">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D213">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D214">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D215">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D216">
-        <v>112</v>
+        <v>17</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D217">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D218">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D219">
-        <v>378</v>
+        <v>112</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D220">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7417,11 +7417,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D221">
-        <v>268</v>
+        <v>70</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7444,16 +7444,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>305</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7476,16 +7476,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7508,16 +7508,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D224">
-        <v>4</v>
+        <v>268</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7545,11 +7545,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D225">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7577,11 +7577,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D226">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7604,16 +7604,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D227">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7636,16 +7636,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D228">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7668,16 +7668,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D229">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7705,11 +7705,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D230">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7737,11 +7737,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D231">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7769,11 +7769,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D232">
-        <v>342</v>
+        <v>61</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D233">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7833,11 +7833,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D234">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7865,11 +7865,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D235">
-        <v>66</v>
+        <v>332</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D236">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D237">
-        <v>36</v>
+        <v>216</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D238">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D239">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D240">
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D241">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D242">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8116,16 +8116,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D243">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8148,16 +8148,16 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8180,16 +8180,16 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D245">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8249,11 +8249,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D247">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8281,11 +8281,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D248">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8313,7 +8313,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D249">
@@ -8345,11 +8345,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D250">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8377,11 +8377,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D251">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8409,22 +8409,118 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="D252">
+        <v>1</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>0</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>LDG</t>
+        </is>
+      </c>
+      <c r="D253">
+        <v>16</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>0</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="D254">
+        <v>27</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>0</v>
+      </c>
+      <c r="G254">
+        <v>0</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="D252">
+      <c r="D255">
         <v>2</v>
       </c>
-      <c r="E252">
-        <v>0</v>
-      </c>
-      <c r="F252">
-        <v>0</v>
-      </c>
-      <c r="G252">
-        <v>0</v>
-      </c>
-      <c r="H252">
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>0</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
+      </c>
+      <c r="H255">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H255"/>
+  <dimension ref="A1:H260"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="D15">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="G15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H15">
-        <v>342</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D29">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D30">
-        <v>395</v>
+        <v>36</v>
       </c>
       <c r="E30">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>395</v>
+        <v>36</v>
       </c>
       <c r="G30">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>395</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D31">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>50</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D32">
-        <v>123</v>
+        <v>439</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F32">
-        <v>123</v>
+        <v>439</v>
       </c>
       <c r="G32">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="H32">
-        <v>123</v>
+        <v>439</v>
       </c>
     </row>
     <row r="33">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D33">
-        <v>412</v>
+        <v>50</v>
       </c>
       <c r="E33">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>412</v>
+        <v>50</v>
       </c>
       <c r="G33">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>412</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34">
@@ -1428,28 +1428,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D34">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F34">
-        <v>16</v>
+        <v>123</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H34">
-        <v>16</v>
+        <v>123</v>
       </c>
     </row>
     <row r="35">
@@ -1460,28 +1460,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>432</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>432</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D36">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <v>1</v>
       </c>
       <c r="H36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D37">
@@ -1561,11 +1561,11 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1588,28 +1588,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D39">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -1620,28 +1620,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D40">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>47</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41">
@@ -1652,16 +1652,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -1716,80 +1716,80 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>6</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D44">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1798,30 +1798,30 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1830,10 +1830,10 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
@@ -1844,16 +1844,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1876,16 +1876,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1913,11 +1913,11 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D50">
@@ -1977,11 +1977,11 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D51">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2009,11 +2009,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2041,11 +2041,11 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2073,11 +2073,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2105,11 +2105,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D55">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2137,11 +2137,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D57">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2201,11 +2201,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2233,11 +2233,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2265,11 +2265,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2297,11 +2297,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D62">
@@ -2356,16 +2356,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2388,16 +2388,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D64">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D65">
@@ -2457,11 +2457,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D66">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D67">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2521,11 +2521,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D69">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2585,11 +2585,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D70">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2617,11 +2617,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D71">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D72">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D73">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D74">
-        <v>83</v>
+        <v>4</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D75">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2777,11 +2777,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D76">
-        <v>245</v>
+        <v>21</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2809,11 +2809,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D77">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D79">
-        <v>56</v>
+        <v>245</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D80">
-        <v>114</v>
+        <v>26</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2937,11 +2937,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D81">
-        <v>715</v>
+        <v>3</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D82">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3001,11 +3001,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D83">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>715</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3060,16 +3060,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D85">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3092,16 +3092,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D86">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3124,16 +3124,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D87">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3161,11 +3161,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D88">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D89">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3225,11 +3225,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D90">
-        <v>154</v>
+        <v>40</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D91">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D92">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D93">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3353,11 +3353,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D94">
-        <v>180</v>
+        <v>216</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D95">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D96">
-        <v>38</v>
+        <v>155</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3449,11 +3449,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D97">
-        <v>241</v>
+        <v>145</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D98">
-        <v>236</v>
+        <v>108</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3513,11 +3513,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D99">
-        <v>61</v>
+        <v>180</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D100">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D101">
-        <v>164</v>
+        <v>38</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D102">
-        <v>22</v>
+        <v>241</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D103">
-        <v>36</v>
+        <v>206</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3673,11 +3673,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D104">
-        <v>192</v>
+        <v>61</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3705,11 +3705,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D105">
-        <v>144</v>
+        <v>9</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3732,16 +3732,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>113</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3764,16 +3764,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D107">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3796,16 +3796,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>170</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3828,16 +3828,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>354</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3860,16 +3860,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3892,16 +3892,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D111">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3924,16 +3924,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D112">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3956,16 +3956,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D113">
-        <v>595</v>
+        <v>1</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3988,16 +3988,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D114">
-        <v>426</v>
+        <v>1</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4020,16 +4020,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D115">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4057,11 +4057,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D116">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4089,11 +4089,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D117">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4121,11 +4121,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D118">
-        <v>613</v>
+        <v>595</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4153,11 +4153,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D119">
-        <v>104</v>
+        <v>426</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4185,11 +4185,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D120">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4217,11 +4217,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D121">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4249,11 +4249,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D122">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D123">
-        <v>687</v>
+        <v>589</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D124">
-        <v>16</v>
+        <v>104</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4345,11 +4345,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D125">
-        <v>718</v>
+        <v>22</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4377,11 +4377,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D126">
-        <v>530</v>
+        <v>96</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4409,11 +4409,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D127">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4441,11 +4441,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D128">
-        <v>168</v>
+        <v>687</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4468,16 +4468,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D129">
-        <v>7</v>
+        <v>718</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4500,16 +4500,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>530</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4532,16 +4532,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D131">
-        <v>70</v>
+        <v>212</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4564,16 +4564,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D132">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4601,11 +4601,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D133">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4633,7 +4633,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D134">
@@ -4665,11 +4665,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D135">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4697,11 +4697,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D136">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4729,11 +4729,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D137">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D138">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D139">
@@ -4825,11 +4825,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D140">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D141">
-        <v>1657</v>
+        <v>6</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4879,21 +4879,21 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D142">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4911,21 +4911,21 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D143">
-        <v>3360</v>
+        <v>11</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4943,21 +4943,21 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D144">
-        <v>8023</v>
+        <v>6</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4975,21 +4975,21 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D145">
-        <v>5</v>
+        <v>1657</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="D146">
-        <v>9900</v>
+        <v>54</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5044,7 +5044,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5053,7 +5053,7 @@
         </is>
       </c>
       <c r="D147">
-        <v>12</v>
+        <v>3173</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5071,21 +5071,21 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>7015</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5103,21 +5103,21 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D149">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5135,21 +5135,21 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D150">
-        <v>2916</v>
+        <v>9900</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5167,21 +5167,21 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D151">
-        <v>3816</v>
+        <v>12</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -5213,7 +5213,7 @@
         </is>
       </c>
       <c r="D152">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5231,21 +5231,21 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D153">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5263,21 +5263,21 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D154">
-        <v>72</v>
+        <v>2880</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5295,21 +5295,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D155">
-        <v>8964</v>
+        <v>3816</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5327,21 +5327,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D156">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5373,7 +5373,7 @@
         </is>
       </c>
       <c r="D157">
-        <v>8100</v>
+        <v>46</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5396,7 +5396,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="D158">
-        <v>14</v>
+        <v>72</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5423,21 +5423,21 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D159">
-        <v>89</v>
+        <v>8748</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5455,21 +5455,21 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D160">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5487,21 +5487,21 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D161">
-        <v>26</v>
+        <v>8064</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5519,21 +5519,21 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D162">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D163">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D164">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5620,16 +5620,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D165">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5652,16 +5652,16 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D166">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5684,16 +5684,16 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D167">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5716,16 +5716,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D168">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5753,11 +5753,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D169">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5785,11 +5785,11 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5817,11 +5817,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D171">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5849,11 +5849,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D172">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5881,11 +5881,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D173">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5913,11 +5913,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D174">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5945,11 +5945,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D175">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5977,11 +5977,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D176">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -6009,11 +6009,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D177">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6041,11 +6041,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D178">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6073,11 +6073,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D179">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6105,11 +6105,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6137,11 +6137,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6169,11 +6169,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D182">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6196,16 +6196,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D183">
-        <v>115</v>
+        <v>13</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6228,16 +6228,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D184">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6260,16 +6260,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D185">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6292,16 +6292,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D186">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6329,11 +6329,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D187">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6361,11 +6361,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D188">
-        <v>101</v>
+        <v>41</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6393,11 +6393,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D189">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6425,11 +6425,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D190">
-        <v>248</v>
+        <v>304</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6457,11 +6457,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D191">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6489,11 +6489,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D192">
-        <v>10</v>
+        <v>101</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6521,11 +6521,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D193">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6553,11 +6553,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D194">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6585,11 +6585,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D195">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6617,11 +6617,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D196">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6649,11 +6649,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D197">
-        <v>182</v>
+        <v>12</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D198">
-        <v>32</v>
+        <v>222</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6713,11 +6713,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D199">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6745,11 +6745,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D200">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6777,11 +6777,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D201">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6809,11 +6809,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D202">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6841,11 +6841,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D203">
-        <v>24</v>
+        <v>204</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6873,11 +6873,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D204">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6905,11 +6905,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D205">
-        <v>12</v>
+        <v>59</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D206">
-        <v>121</v>
+        <v>6</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6969,11 +6969,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D207">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -6996,16 +6996,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D208">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7028,16 +7028,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D209">
-        <v>295</v>
+        <v>12</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7060,16 +7060,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D210">
-        <v>420</v>
+        <v>121</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7092,16 +7092,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D211">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D212">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D213">
-        <v>170</v>
+        <v>295</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D214">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D215">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D216">
-        <v>17</v>
+        <v>146</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D217">
-        <v>18</v>
+        <v>170</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D218">
-        <v>62</v>
+        <v>120</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D219">
-        <v>112</v>
+        <v>30</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D220">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7417,11 +7417,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D221">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7449,11 +7449,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D222">
-        <v>305</v>
+        <v>62</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D223">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7513,11 +7513,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D224">
-        <v>268</v>
+        <v>125</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7540,16 +7540,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D225">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D226">
-        <v>2</v>
+        <v>305</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7604,16 +7604,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D227">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7636,16 +7636,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D228">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7668,16 +7668,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D229">
-        <v>24</v>
+        <v>286</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7700,16 +7700,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D230">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7732,16 +7732,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D231">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7764,16 +7764,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D232">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7796,16 +7796,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D233">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7828,16 +7828,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D234">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7860,16 +7860,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D235">
-        <v>332</v>
+        <v>24</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D236">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D237">
-        <v>216</v>
+        <v>76</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D238">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D239">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,7 +8025,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D240">
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D241">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D242">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D243">
-        <v>36</v>
+        <v>216</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D244">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D245">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8212,16 +8212,16 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D246">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8244,16 +8244,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8276,16 +8276,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8308,16 +8308,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8340,16 +8340,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D250">
-        <v>164</v>
+        <v>60</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8377,7 +8377,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D251">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D252">
@@ -8441,11 +8441,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D253">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8473,11 +8473,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D254">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8505,22 +8505,182 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="D255">
+        <v>164</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>0</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>HNI</t>
+        </is>
+      </c>
+      <c r="D256">
+        <v>2</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>0</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>0</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>LDG</t>
+        </is>
+      </c>
+      <c r="D258">
+        <v>16</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>0</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="D259">
+        <v>27</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>0</v>
+      </c>
+      <c r="G259">
+        <v>0</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="D255">
+      <c r="D260">
         <v>2</v>
       </c>
-      <c r="E255">
-        <v>0</v>
-      </c>
-      <c r="F255">
-        <v>0</v>
-      </c>
-      <c r="G255">
-        <v>0</v>
-      </c>
-      <c r="H255">
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>0</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H260"/>
+  <dimension ref="A1:H261"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
@@ -829,13 +829,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="G15">
         <v>12</v>
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="D26">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
@@ -1245,7 +1245,7 @@
         </is>
       </c>
       <c r="D28">
-        <v>186</v>
+        <v>341</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -1376,16 +1376,16 @@
         <v>439</v>
       </c>
       <c r="E32">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F32">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="G32">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H32">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="33">
@@ -1469,19 +1469,19 @@
         </is>
       </c>
       <c r="D35">
-        <v>432</v>
+        <v>563</v>
       </c>
       <c r="E35">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F35">
-        <v>432</v>
+        <v>553</v>
       </c>
       <c r="G35">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H35">
-        <v>432</v>
+        <v>553</v>
       </c>
     </row>
     <row r="36">
@@ -1664,16 +1664,16 @@
         <v>12</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1757,19 +1757,19 @@
         </is>
       </c>
       <c r="D44">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>20</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
@@ -2489,11 +2489,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D67">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2521,11 +2521,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D72">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2813,7 +2813,7 @@
         </is>
       </c>
       <c r="D77">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         </is>
       </c>
       <c r="D78">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="D79">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="D83">
-        <v>114</v>
+        <v>3</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3101,7 +3101,7 @@
         </is>
       </c>
       <c r="D86">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3225,11 +3225,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D90">
-        <v>40</v>
+        <v>216</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D91">
-        <v>180</v>
+        <v>40</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D92">
-        <v>268</v>
+        <v>180</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D93">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3353,11 +3353,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D94">
-        <v>216</v>
+        <v>110</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D95">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D96">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="D98">
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3581,7 +3581,7 @@
         </is>
       </c>
       <c r="D101">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3645,7 +3645,7 @@
         </is>
       </c>
       <c r="D103">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3677,7 +3677,7 @@
         </is>
       </c>
       <c r="D104">
-        <v>61</v>
+        <v>241</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="D107">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3833,11 +3833,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D109">
-        <v>354</v>
+        <v>18</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D110">
-        <v>36</v>
+        <v>707</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3892,16 +3892,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3924,16 +3924,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D112">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4025,11 +4025,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4052,16 +4052,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D116">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4084,16 +4084,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D117">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4121,11 +4121,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D118">
-        <v>595</v>
+        <v>99</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4153,11 +4153,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D119">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4185,11 +4185,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D120">
-        <v>56</v>
+        <v>543</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4217,11 +4217,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D121">
-        <v>72</v>
+        <v>426</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4249,11 +4249,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D122">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D123">
-        <v>589</v>
+        <v>72</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D124">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4345,11 +4345,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D125">
-        <v>22</v>
+        <v>589</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4377,11 +4377,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D126">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4409,11 +4409,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D127">
-        <v>242</v>
+        <v>22</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4441,11 +4441,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D128">
-        <v>687</v>
+        <v>160</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D129">
-        <v>718</v>
+        <v>242</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4505,11 +4505,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D130">
-        <v>530</v>
+        <v>687</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D131">
-        <v>212</v>
+        <v>626</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4569,11 +4569,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D132">
-        <v>154</v>
+        <v>516</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4596,16 +4596,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D133">
-        <v>7</v>
+        <v>192</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4628,16 +4628,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>154</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4665,11 +4665,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D135">
-        <v>70</v>
+        <v>7</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4697,11 +4697,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D136">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4729,11 +4729,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D137">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4761,11 +4761,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4793,11 +4793,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D139">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4825,11 +4825,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D140">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D141">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4921,11 +4921,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D143">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D144">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4985,11 +4985,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D145">
-        <v>1657</v>
+        <v>11</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5007,21 +5007,21 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D146">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5039,21 +5039,21 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D147">
-        <v>3173</v>
+        <v>1657</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="D148">
-        <v>7015</v>
+        <v>54</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="D149">
-        <v>5</v>
+        <v>3041</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5149,7 +5149,7 @@
         </is>
       </c>
       <c r="D150">
-        <v>9900</v>
+        <v>6619</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="D151">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5199,21 +5199,21 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>9756</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5231,21 +5231,21 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="D154">
-        <v>2880</v>
+        <v>1</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5309,7 +5309,7 @@
         </is>
       </c>
       <c r="D155">
-        <v>3816</v>
+        <v>1</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5341,7 +5341,7 @@
         </is>
       </c>
       <c r="D156">
-        <v>8</v>
+        <v>2665</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5359,21 +5359,21 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D157">
-        <v>46</v>
+        <v>3816</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5391,21 +5391,21 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D158">
-        <v>72</v>
+        <v>8</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="D159">
-        <v>8748</v>
+        <v>46</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="D160">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5492,7 +5492,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="D161">
-        <v>8064</v>
+        <v>8352</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="D162">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5551,21 +5551,21 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D163">
-        <v>89</v>
+        <v>7992</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5583,21 +5583,21 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D164">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5625,11 +5625,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D165">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5657,11 +5657,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D166">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D167">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5721,11 +5721,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D168">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5748,16 +5748,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5780,16 +5780,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5817,11 +5817,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D171">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5849,11 +5849,11 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D172">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5881,11 +5881,11 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D173">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5913,11 +5913,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5945,11 +5945,11 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D175">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5977,11 +5977,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D176">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -6009,11 +6009,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D177">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6041,11 +6041,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D178">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6073,11 +6073,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D179">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6105,11 +6105,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6137,11 +6137,11 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6169,11 +6169,11 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D182">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6201,11 +6201,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D183">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6233,11 +6233,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6265,11 +6265,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D185">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6297,11 +6297,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D186">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6324,16 +6324,16 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D187">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6361,11 +6361,11 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D188">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6393,11 +6393,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D189">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6425,11 +6425,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D190">
-        <v>304</v>
+        <v>7</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6457,11 +6457,11 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D191">
-        <v>30</v>
+        <v>304</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6489,11 +6489,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D192">
-        <v>101</v>
+        <v>30</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6521,11 +6521,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D193">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6553,11 +6553,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D194">
-        <v>226</v>
+        <v>81</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6585,11 +6585,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D195">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6617,11 +6617,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D196">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6649,11 +6649,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D197">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D198">
-        <v>222</v>
+        <v>12</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6713,11 +6713,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D199">
-        <v>1</v>
+        <v>222</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6745,11 +6745,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D200">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6777,11 +6777,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D201">
-        <v>182</v>
+        <v>8</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6809,11 +6809,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D202">
-        <v>32</v>
+        <v>182</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6841,11 +6841,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D203">
-        <v>204</v>
+        <v>32</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6873,11 +6873,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D204">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6905,11 +6905,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D205">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D206">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6969,11 +6969,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D207">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -7001,11 +7001,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D208">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7033,11 +7033,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D209">
-        <v>12</v>
+        <v>129</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7065,11 +7065,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D210">
-        <v>121</v>
+        <v>12</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7097,11 +7097,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D211">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7124,16 +7124,16 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D212">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D213">
-        <v>295</v>
+        <v>90</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D214">
-        <v>420</v>
+        <v>295</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D215">
-        <v>91</v>
+        <v>402</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D216">
-        <v>146</v>
+        <v>91</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D217">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D218">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D219">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D220">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7417,11 +7417,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D221">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7449,11 +7449,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D222">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D223">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7513,11 +7513,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D224">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7545,11 +7545,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D225">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7577,11 +7577,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D226">
-        <v>305</v>
+        <v>70</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7609,11 +7609,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D227">
-        <v>41</v>
+        <v>305</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7641,11 +7641,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D228">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7673,11 +7673,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D229">
-        <v>286</v>
+        <v>10</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7705,11 +7705,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D230">
-        <v>72</v>
+        <v>300</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7732,16 +7732,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D232">
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D233">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7833,11 +7833,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D234">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7865,11 +7865,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D235">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7892,16 +7892,16 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D236">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D237">
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D238">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D239">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D240">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D241">
-        <v>332</v>
+        <v>36</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D242">
-        <v>36</v>
+        <v>332</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D243">
-        <v>216</v>
+        <v>36</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D244">
-        <v>66</v>
+        <v>216</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D245">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D246">
-        <v>36</v>
+        <v>100</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8249,11 +8249,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D247">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8281,11 +8281,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D248">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8313,11 +8313,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D249">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8345,11 +8345,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D250">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8372,16 +8372,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D251">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8409,11 +8409,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D253">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D254">
@@ -8505,11 +8505,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D255">
-        <v>164</v>
+        <v>1</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8537,11 +8537,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D256">
-        <v>2</v>
+        <v>164</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8569,11 +8569,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -8601,11 +8601,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D258">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8633,11 +8633,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D259">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -8665,22 +8665,54 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="D260">
+        <v>27</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>0</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
           <t>TNN</t>
         </is>
       </c>
-      <c r="D260">
+      <c r="D261">
         <v>2</v>
       </c>
-      <c r="E260">
-        <v>0</v>
-      </c>
-      <c r="F260">
-        <v>0</v>
-      </c>
-      <c r="G260">
-        <v>0</v>
-      </c>
-      <c r="H260">
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H261"/>
+  <dimension ref="A1:H289"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="D6">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>75</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="D7">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -678,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -729,23 +729,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>4</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -761,23 +761,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -793,23 +793,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D14">
-        <v>3</v>
+        <v>663</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
@@ -825,23 +825,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D15">
-        <v>447</v>
+        <v>25</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F15">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="G15">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>322</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -857,23 +857,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -889,23 +889,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="G17">
         <v>1</v>
       </c>
       <c r="H17">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -921,23 +921,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D18">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>13</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -953,23 +953,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H19">
-        <v>30</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20">
@@ -985,23 +985,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D20">
-        <v>200</v>
+        <v>138</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>156</v>
+        <v>118</v>
       </c>
       <c r="G20">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>156</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D21">
@@ -1027,10 +1027,10 @@
         <v>1</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H21">
         <v>18</v>
@@ -1049,23 +1049,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D22">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F22">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H22">
-        <v>28</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -1081,23 +1081,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
       <c r="F23">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
@@ -1113,23 +1113,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D24">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>114</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1149,19 +1149,19 @@
         </is>
       </c>
       <c r="D25">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="G25">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>75</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -1181,19 +1181,19 @@
         </is>
       </c>
       <c r="D26">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1213,19 +1213,19 @@
         </is>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H27">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28">
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="D28">
-        <v>341</v>
+        <v>737</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F28">
-        <v>131</v>
+        <v>335</v>
       </c>
       <c r="G28">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H28">
-        <v>148</v>
+        <v>550</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G29">
         <v>1</v>
       </c>
       <c r="H29">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>308</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F31">
-        <v>12</v>
+        <v>276</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="H31">
-        <v>12</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D32">
-        <v>439</v>
+        <v>50</v>
       </c>
       <c r="E32">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>431</v>
+        <v>50</v>
       </c>
       <c r="G32">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>431</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D33">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F33">
-        <v>50</v>
+        <v>182</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H33">
-        <v>50</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34">
@@ -1433,23 +1433,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D34">
-        <v>123</v>
+        <v>1293</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="F34">
-        <v>123</v>
+        <v>1211</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="H34">
-        <v>123</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="35">
@@ -1465,23 +1465,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D35">
-        <v>563</v>
+        <v>8</v>
       </c>
       <c r="E35">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F35">
-        <v>553</v>
+        <v>8</v>
       </c>
       <c r="G35">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="H35">
-        <v>553</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
@@ -1492,28 +1492,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -1524,28 +1524,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D37">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -1561,23 +1561,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1593,23 +1593,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>2</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -1625,23 +1625,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D40">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1689,23 +1689,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G42">
         <v>1</v>
       </c>
       <c r="H42">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
@@ -1721,23 +1721,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D43">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -1753,23 +1753,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D44">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>36</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
@@ -1780,28 +1780,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>567</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>370</v>
       </c>
       <c r="G45">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H45">
-        <v>5</v>
+        <v>394</v>
       </c>
     </row>
     <row r="46">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1821,83 +1821,83 @@
         </is>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>232</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H46">
-        <v>6</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D47">
-        <v>24</v>
+        <v>72</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D48">
         <v>4</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -1908,16 +1908,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D49">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -1940,16 +1940,16 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -1972,16 +1972,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2009,11 +2009,11 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D53">
@@ -2073,11 +2073,11 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D54">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2105,11 +2105,11 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2137,11 +2137,11 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2169,11 +2169,11 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2201,11 +2201,11 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D58">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2233,11 +2233,11 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2265,11 +2265,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D60">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2297,11 +2297,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2329,11 +2329,11 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2361,11 +2361,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D64">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D65">
@@ -2452,16 +2452,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D66">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2484,16 +2484,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2521,11 +2521,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D68">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D69">
-        <v>175</v>
+        <v>12</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2585,11 +2585,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D70">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2617,11 +2617,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D71">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D72">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D73">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D75">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2777,11 +2777,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D76">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2809,11 +2809,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D77">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D78">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D79">
-        <v>233</v>
+        <v>5</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D80">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2937,11 +2937,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D81">
-        <v>3</v>
+        <v>73</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D82">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3001,11 +3001,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D84">
-        <v>715</v>
+        <v>1</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3065,11 +3065,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D85">
-        <v>11</v>
+        <v>524</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D86">
-        <v>68</v>
+        <v>11</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3156,16 +3156,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D88">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D89">
-        <v>26</v>
+        <v>155</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3225,11 +3225,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D90">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D91">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D92">
-        <v>180</v>
+        <v>107</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D93">
-        <v>265</v>
+        <v>147</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3353,11 +3353,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D94">
-        <v>110</v>
+        <v>216</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D95">
-        <v>216</v>
+        <v>89</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D96">
-        <v>154</v>
+        <v>90</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3449,11 +3449,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D97">
-        <v>145</v>
+        <v>396</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D98">
-        <v>288</v>
+        <v>368</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3513,11 +3513,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D99">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D100">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D101">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D102">
-        <v>241</v>
+        <v>438</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D103">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3673,11 +3673,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D104">
-        <v>241</v>
+        <v>36</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3705,11 +3705,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D105">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D106">
-        <v>113</v>
+        <v>197</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D107">
-        <v>41</v>
+        <v>322</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D108">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3833,11 +3833,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D109">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D110">
-        <v>707</v>
+        <v>194</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D111">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D112">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3956,16 +3956,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3988,16 +3988,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D114">
-        <v>3</v>
+        <v>437</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4020,16 +4020,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>304</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D116">
@@ -4084,16 +4084,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D117">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4116,16 +4116,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D118">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4148,16 +4148,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D119">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4180,16 +4180,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D120">
-        <v>543</v>
+        <v>2</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4212,16 +4212,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D121">
-        <v>426</v>
+        <v>1</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4244,16 +4244,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D122">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4276,16 +4276,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D123">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4308,16 +4308,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 625</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D124">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4340,16 +4340,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D125">
-        <v>589</v>
+        <v>7</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4372,16 +4372,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D126">
-        <v>104</v>
+        <v>1</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4404,16 +4404,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D127">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4436,16 +4436,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D128">
-        <v>160</v>
+        <v>3</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4468,16 +4468,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D129">
-        <v>242</v>
+        <v>10</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4500,16 +4500,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D130">
-        <v>687</v>
+        <v>1</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4532,16 +4532,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D131">
-        <v>626</v>
+        <v>8</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4564,16 +4564,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D132">
-        <v>516</v>
+        <v>2</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4596,16 +4596,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D133">
-        <v>192</v>
+        <v>3</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4628,16 +4628,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D134">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4660,16 +4660,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D135">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4692,16 +4692,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4724,16 +4724,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D137">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4756,16 +4756,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D138">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4788,16 +4788,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D139">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4820,16 +4820,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4852,16 +4852,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D141">
-        <v>11</v>
+        <v>96</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4884,16 +4884,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D142">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4916,16 +4916,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D143">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4948,16 +4948,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4980,16 +4980,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D145">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5012,16 +5012,16 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D146">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5044,16 +5044,16 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D147">
-        <v>1657</v>
+        <v>26</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5071,21 +5071,21 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D148">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5103,21 +5103,21 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D149">
-        <v>3041</v>
+        <v>236</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5135,21 +5135,21 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D150">
-        <v>6619</v>
+        <v>448</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5167,21 +5167,21 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D151">
-        <v>5</v>
+        <v>402</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5199,7 +5199,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5209,11 +5209,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D152">
-        <v>9756</v>
+        <v>335</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5231,21 +5231,21 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D153">
-        <v>12</v>
+        <v>374</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5263,17 +5263,17 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D154">
@@ -5295,21 +5295,21 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D155">
-        <v>1</v>
+        <v>298</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5327,21 +5327,21 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D156">
-        <v>2665</v>
+        <v>70</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5359,21 +5359,21 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D157">
-        <v>3816</v>
+        <v>1</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5391,7 +5391,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D158">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5423,21 +5423,21 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D159">
-        <v>46</v>
+        <v>1646</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5455,21 +5455,21 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D160">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5487,21 +5487,21 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D161">
-        <v>8352</v>
+        <v>2529</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5519,21 +5519,21 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D162">
-        <v>19</v>
+        <v>9255</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5551,21 +5551,21 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D163">
-        <v>7992</v>
+        <v>4</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5583,21 +5583,21 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D164">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5615,21 +5615,21 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D165">
-        <v>89</v>
+        <v>8732</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5647,17 +5647,17 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D166">
@@ -5679,21 +5679,21 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D167">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5711,21 +5711,21 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D168">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5743,21 +5743,21 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D169">
-        <v>30</v>
+        <v>4429</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5775,21 +5775,21 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Jinko 535</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D170">
-        <v>51</v>
+        <v>3</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5807,21 +5807,21 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D171">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5839,21 +5839,21 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D172">
-        <v>5</v>
+        <v>3348</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5871,21 +5871,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5913,11 +5913,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D174">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5935,21 +5935,21 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D175">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5967,21 +5967,21 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D176">
-        <v>12</v>
+        <v>5940</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5999,21 +5999,21 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Jinko 545</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D177">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6031,21 +6031,21 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D178">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6063,21 +6063,21 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D179">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6095,21 +6095,21 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D180">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6127,21 +6127,21 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D181">
-        <v>2</v>
+        <v>6408</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6159,21 +6159,21 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D182">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6196,16 +6196,16 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D183">
-        <v>14</v>
+        <v>141</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6228,16 +6228,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D184">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6260,16 +6260,16 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6292,16 +6292,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D186">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="D188">
-        <v>115</v>
+        <v>4</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6420,16 +6420,16 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D190">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6452,16 +6452,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D191">
-        <v>304</v>
+        <v>14</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6484,16 +6484,16 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D192">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6516,16 +6516,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D193">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6548,16 +6548,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D194">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6580,16 +6580,16 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D195">
-        <v>226</v>
+        <v>4</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6612,16 +6612,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D196">
-        <v>89</v>
+        <v>7</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6644,16 +6644,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D197">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6676,16 +6676,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D198">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6708,16 +6708,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D199">
-        <v>222</v>
+        <v>3</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6740,16 +6740,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6772,16 +6772,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D201">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6804,16 +6804,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D202">
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6836,16 +6836,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D203">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6868,16 +6868,16 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D204">
-        <v>204</v>
+        <v>17</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6905,11 +6905,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D205">
-        <v>28</v>
+        <v>115</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D206">
-        <v>59</v>
+        <v>34</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6969,11 +6969,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D207">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -7001,11 +7001,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D208">
-        <v>24</v>
+        <v>304</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7033,11 +7033,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D209">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7065,11 +7065,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D210">
-        <v>12</v>
+        <v>160</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7097,11 +7097,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D211">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D212">
-        <v>114</v>
+        <v>225</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7156,16 +7156,16 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D213">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7188,16 +7188,16 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D214">
-        <v>295</v>
+        <v>10</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7220,16 +7220,16 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D215">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7252,16 +7252,16 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D216">
-        <v>91</v>
+        <v>222</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7284,16 +7284,16 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D217">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7316,16 +7316,16 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D218">
-        <v>170</v>
+        <v>8</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7348,16 +7348,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D219">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7380,16 +7380,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D220">
-        <v>30</v>
+        <v>194</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7412,16 +7412,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D221">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7444,16 +7444,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D222">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7476,16 +7476,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D223">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7508,16 +7508,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D224">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7540,16 +7540,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D225">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D226">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7604,16 +7604,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D227">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7636,16 +7636,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D228">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7668,16 +7668,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D229">
-        <v>10</v>
+        <v>151</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7700,16 +7700,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D230">
-        <v>300</v>
+        <v>114</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7737,11 +7737,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D231">
-        <v>72</v>
+        <v>311</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7764,16 +7764,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D232">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7796,16 +7796,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D233">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7828,16 +7828,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D234">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7860,16 +7860,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D235">
-        <v>48</v>
+        <v>148</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7892,16 +7892,16 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D236">
-        <v>24</v>
+        <v>841</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7924,16 +7924,16 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D237">
-        <v>76</v>
+        <v>273</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7956,16 +7956,16 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D238">
-        <v>76</v>
+        <v>217</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7988,16 +7988,16 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D239">
-        <v>61</v>
+        <v>438</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8020,16 +8020,16 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D240">
-        <v>32</v>
+        <v>308</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8052,16 +8052,16 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D241">
-        <v>36</v>
+        <v>244</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8084,16 +8084,16 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D242">
-        <v>332</v>
+        <v>14</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8116,16 +8116,16 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D243">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8148,16 +8148,16 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D244">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8180,16 +8180,16 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D245">
-        <v>66</v>
+        <v>147</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8212,16 +8212,16 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D246">
-        <v>100</v>
+        <v>273</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8244,16 +8244,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D247">
-        <v>36</v>
+        <v>227</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8276,16 +8276,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D248">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8308,16 +8308,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D249">
-        <v>36</v>
+        <v>800</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8340,16 +8340,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D250">
-        <v>58</v>
+        <v>237</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8372,16 +8372,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D251">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8404,16 +8404,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D252">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8436,16 +8436,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>148</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8468,16 +8468,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8500,16 +8500,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>128</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8532,16 +8532,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D256">
-        <v>164</v>
+        <v>18</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8564,16 +8564,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -8596,16 +8596,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8628,16 +8628,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D259">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -8660,16 +8660,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D260">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -8692,27 +8692,923 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
+          <t>Jinko 585</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="D261">
+        <v>7</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>0</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Longi 585</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>BNH</t>
+        </is>
+      </c>
+      <c r="D262">
+        <v>2</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>0</v>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Longi 585</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="D263">
+        <v>1</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>0</v>
+      </c>
+      <c r="G263">
+        <v>0</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Longi 585</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>0</v>
+      </c>
+      <c r="G264">
+        <v>0</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Longi 585</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>0</v>
+      </c>
+      <c r="G265">
+        <v>0</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Longi 585</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="D266">
+        <v>2</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>0</v>
+      </c>
+      <c r="G266">
+        <v>0</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Longi 615</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="D267">
+        <v>1</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>0</v>
+      </c>
+      <c r="G267">
+        <v>0</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Longi 615</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>KHA</t>
+        </is>
+      </c>
+      <c r="D268">
+        <v>4</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>0</v>
+      </c>
+      <c r="G268">
+        <v>0</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Longi 615</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>NBH</t>
+        </is>
+      </c>
+      <c r="D269">
+        <v>46</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
+      <c r="G269">
+        <v>0</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Longi 615</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="D270">
+        <v>24</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>0</v>
+      </c>
+      <c r="G270">
+        <v>0</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>AGG</t>
+        </is>
+      </c>
+      <c r="D271">
+        <v>244</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>0</v>
+      </c>
+      <c r="G271">
+        <v>0</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>CMU</t>
+        </is>
+      </c>
+      <c r="D272">
+        <v>96</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
+      </c>
+      <c r="G272">
+        <v>0</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>CTO</t>
+        </is>
+      </c>
+      <c r="D273">
+        <v>341</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
+      <c r="G273">
+        <v>0</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>DLK</t>
+        </is>
+      </c>
+      <c r="D274">
+        <v>141</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>0</v>
+      </c>
+      <c r="G274">
+        <v>0</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>DNG</t>
+        </is>
+      </c>
+      <c r="D275">
+        <v>130</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>0</v>
+      </c>
+      <c r="G275">
+        <v>0</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>DNI</t>
+        </is>
+      </c>
+      <c r="D276">
+        <v>36</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>0</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>DTP</t>
+        </is>
+      </c>
+      <c r="D277">
+        <v>600</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>0</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>GLI</t>
+        </is>
+      </c>
+      <c r="D278">
+        <v>62</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>0</v>
+      </c>
+      <c r="G278">
+        <v>0</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>HCM</t>
+        </is>
+      </c>
+      <c r="D279">
+        <v>360</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>0</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>HYN</t>
+        </is>
+      </c>
+      <c r="D280">
+        <v>360</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+      <c r="G280">
+        <v>0</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>LSN</t>
+        </is>
+      </c>
+      <c r="D281">
+        <v>10</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>0</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>NBH</t>
+        </is>
+      </c>
+      <c r="D282">
+        <v>66</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>PTO</t>
+        </is>
+      </c>
+      <c r="D283">
+        <v>331</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>0</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>QNI</t>
+        </is>
+      </c>
+      <c r="D284">
+        <v>56</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>0</v>
+      </c>
+      <c r="G284">
+        <v>0</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="D285">
+        <v>302</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>0</v>
+      </c>
+      <c r="G285">
+        <v>0</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="D286">
+        <v>36</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+      <c r="G286">
+        <v>0</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="D287">
+        <v>293</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>0</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="D288">
+        <v>36</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>0</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
           <t>TCT_Pin khác</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>TNN</t>
-        </is>
-      </c>
-      <c r="D261">
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>QNH</t>
+        </is>
+      </c>
+      <c r="D289">
         <v>2</v>
       </c>
-      <c r="E261">
-        <v>0</v>
-      </c>
-      <c r="F261">
-        <v>0</v>
-      </c>
-      <c r="G261">
-        <v>0</v>
-      </c>
-      <c r="H261">
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H301"/>
+  <dimension ref="A1:H304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -409,11 +409,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -422,10 +422,10 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -441,23 +441,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -473,23 +473,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D4">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -500,28 +500,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -537,23 +537,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D6">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -569,11 +569,11 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -601,23 +601,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -633,23 +633,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D9">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -665,23 +665,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D11">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -729,11 +729,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D12">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -756,28 +756,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D13">
         <v>24</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -793,23 +793,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D14">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -825,23 +825,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D15">
-        <v>571</v>
+        <v>12</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G15">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -857,23 +857,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D16">
-        <v>25</v>
+        <v>559</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>25</v>
+        <v>71</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H16">
-        <v>25</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17">
@@ -889,23 +889,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D17">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -921,23 +921,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D18">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
@@ -953,14 +953,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D19">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19">
         <v>28</v>
@@ -969,7 +969,7 @@
         <v>2</v>
       </c>
       <c r="H19">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -985,23 +985,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D20">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -1017,23 +1017,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="G21">
         <v>1</v>
       </c>
       <c r="H21">
-        <v>2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
@@ -1049,23 +1049,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D22">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>215</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>215</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1081,23 +1081,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D23">
-        <v>16</v>
+        <v>225</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F23">
-        <v>16</v>
+        <v>215</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H23">
-        <v>16</v>
+        <v>215</v>
       </c>
     </row>
     <row r="24">
@@ -1108,28 +1108,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D24">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="G24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>64</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -1145,23 +1145,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D25">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>8</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D26">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="E26">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>500</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>500</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D27">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D28">
-        <v>109</v>
+        <v>439</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F28">
-        <v>43</v>
+        <v>375</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="H28">
-        <v>43</v>
+        <v>375</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D29">
-        <v>614</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>143</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>402</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D30">
-        <v>68</v>
+        <v>110</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D31">
-        <v>46</v>
+        <v>668</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F31">
-        <v>20</v>
+        <v>197</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H31">
-        <v>20</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D32">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>24</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D33">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="E33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1433,23 +1433,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D34">
-        <v>140</v>
+        <v>12</v>
       </c>
       <c r="E34">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>46</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
@@ -1465,23 +1465,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D35">
-        <v>16</v>
+        <v>157</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H35">
-        <v>16</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D36">
-        <v>541</v>
+        <v>132</v>
       </c>
       <c r="E36">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="F36">
-        <v>491</v>
+        <v>38</v>
       </c>
       <c r="G36">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>491</v>
+        <v>38</v>
       </c>
     </row>
     <row r="37">
@@ -1529,23 +1529,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D37">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G37">
         <v>1</v>
       </c>
       <c r="H37">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="38">
@@ -1561,23 +1561,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D38">
-        <v>1953</v>
+        <v>514</v>
       </c>
       <c r="E38">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="F38">
-        <v>1643</v>
+        <v>448</v>
       </c>
       <c r="G38">
-        <v>87</v>
+        <v>21</v>
       </c>
       <c r="H38">
-        <v>1643</v>
+        <v>448</v>
       </c>
     </row>
     <row r="39">
@@ -1593,23 +1593,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D39">
         <v>12</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -1620,28 +1620,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D40">
-        <v>8</v>
+        <v>1812</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="F40">
-        <v>8</v>
+        <v>1500</v>
       </c>
       <c r="G40">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="H40">
-        <v>8</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="41">
@@ -1652,16 +1652,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43">
@@ -1716,16 +1716,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1748,28 +1748,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D44">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H44">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -1780,16 +1780,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -1817,23 +1817,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D46">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="47">
@@ -1844,28 +1844,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D47">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H47">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1876,16 +1876,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1913,23 +1913,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D49">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50">
@@ -1945,23 +1945,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D50">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -1977,23 +1977,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D51">
-        <v>448</v>
+        <v>14</v>
       </c>
       <c r="E51">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F51">
-        <v>117</v>
+        <v>14</v>
       </c>
       <c r="G51">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H51">
-        <v>221</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52">
@@ -2009,23 +2009,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D52">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F52">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H52">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
@@ -2041,23 +2041,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D53">
-        <v>626</v>
+        <v>647</v>
       </c>
       <c r="E53">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F53">
-        <v>612</v>
+        <v>316</v>
       </c>
       <c r="G53">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="H53">
-        <v>612</v>
+        <v>420</v>
       </c>
     </row>
     <row r="54">
@@ -2073,23 +2073,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D54">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
@@ -2105,23 +2105,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D55">
-        <v>268</v>
+        <v>693</v>
       </c>
       <c r="E55">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F55">
-        <v>250</v>
+        <v>665</v>
       </c>
       <c r="G55">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H55">
-        <v>250</v>
+        <v>665</v>
       </c>
     </row>
     <row r="56">
@@ -2137,23 +2137,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D56">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="E56">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="G56">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>167</v>
+        <v>16</v>
       </c>
     </row>
     <row r="57">
@@ -2169,87 +2169,87 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D57">
-        <v>78</v>
+        <v>352</v>
       </c>
       <c r="E57">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F57">
-        <v>54</v>
+        <v>310</v>
       </c>
       <c r="G57">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H57">
-        <v>54</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D58">
-        <v>12</v>
+        <v>197</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F58">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="G58">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H58">
-        <v>0</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D59">
-        <v>21</v>
+        <v>78</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60">
@@ -2265,11 +2265,11 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2292,16 +2292,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D61">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2324,16 +2324,16 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2361,11 +2361,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D63">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2425,11 +2425,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2457,11 +2457,11 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D66">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D67">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2521,11 +2521,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D69">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2585,11 +2585,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2617,11 +2617,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D72">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D73">
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D74">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2740,16 +2740,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2772,16 +2772,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D76">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D77">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D78">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D79">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D80">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2937,11 +2937,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D81">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3001,11 +3001,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D83">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D84">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3065,11 +3065,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D85">
-        <v>748</v>
+        <v>5</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D87">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3161,11 +3161,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D88">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D89">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3225,11 +3225,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3252,16 +3252,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3284,16 +3284,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D92">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D93">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3353,11 +3353,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D94">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D96">
-        <v>153</v>
+        <v>5</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3449,11 +3449,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D97">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D98">
-        <v>174</v>
+        <v>133</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3513,11 +3513,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D99">
-        <v>419</v>
+        <v>13</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D100">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D101">
-        <v>7</v>
+        <v>408</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D102">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D103">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3673,11 +3673,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D104">
-        <v>490</v>
+        <v>26</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3705,11 +3705,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D105">
-        <v>312</v>
+        <v>120</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>490</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D107">
-        <v>326</v>
+        <v>296</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D108">
-        <v>753</v>
+        <v>1</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3833,11 +3833,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D109">
-        <v>365</v>
+        <v>252</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>753</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D111">
-        <v>140</v>
+        <v>1661</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D112">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D113">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D114">
-        <v>26</v>
+        <v>343</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4025,11 +4025,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D115">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4057,11 +4057,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D116">
-        <v>257</v>
+        <v>18</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4089,11 +4089,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D117">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4116,16 +4116,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4148,16 +4148,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D119">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D120">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D121">
@@ -4249,11 +4249,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4345,11 +4345,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4372,16 +4372,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jinko 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D126">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4404,16 +4404,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D127">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4436,16 +4436,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 625</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D129">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4505,11 +4505,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D130">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D131">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4569,11 +4569,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4601,11 +4601,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D133">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4628,16 +4628,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4660,16 +4660,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D135">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4697,11 +4697,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4729,11 +4729,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4761,11 +4761,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4788,16 +4788,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D139">
-        <v>230</v>
+        <v>1</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4820,16 +4820,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D140">
-        <v>212</v>
+        <v>2</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D141">
-        <v>144</v>
+        <v>840</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D142">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4921,11 +4921,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D143">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D144">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4985,11 +4985,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D145">
-        <v>102</v>
+        <v>3</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5017,11 +5017,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D146">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5049,11 +5049,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D147">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D148">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D149">
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5177,11 +5177,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D151">
-        <v>148</v>
+        <v>42</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D152">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5241,11 +5241,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D153">
-        <v>144</v>
+        <v>1</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D154">
-        <v>36</v>
+        <v>97</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D155">
-        <v>170</v>
+        <v>22</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5337,11 +5337,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D156">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D157">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D158">
-        <v>117</v>
+        <v>170</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D159">
-        <v>98</v>
+        <v>186</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5465,11 +5465,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D160">
-        <v>472</v>
+        <v>19</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D161">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D162">
-        <v>507</v>
+        <v>66</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D163">
-        <v>168</v>
+        <v>508</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D164">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5625,11 +5625,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D165">
-        <v>54</v>
+        <v>436</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5657,11 +5657,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D166">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D167">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5716,16 +5716,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D168">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5748,16 +5748,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5780,16 +5780,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D170">
-        <v>1188</v>
+        <v>115</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5817,11 +5817,11 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D171">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5839,21 +5839,21 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D172">
-        <v>18</v>
+        <v>1188</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5871,21 +5871,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D173">
-        <v>330</v>
+        <v>5</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="D175">
-        <v>4</v>
+        <v>330</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="D176">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="D177">
-        <v>2460</v>
+        <v>4</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6063,21 +6063,21 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>2064</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6095,21 +6095,21 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="D181">
-        <v>865</v>
+        <v>1</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jinko 535</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="D182">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>1</v>
+        <v>649</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 535</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6237,7 +6237,7 @@
         </is>
       </c>
       <c r="D184">
-        <v>2016</v>
+        <v>3</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6287,21 +6287,21 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D186">
-        <v>10</v>
+        <v>1980</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6319,21 +6319,21 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D187">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="D188">
-        <v>468</v>
+        <v>10</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Jinko 545</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>2</v>
+        <v>324</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 545</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="D191">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="D192">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="D193">
-        <v>900</v>
+        <v>5</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6548,7 +6548,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -6557,7 +6557,7 @@
         </is>
       </c>
       <c r="D194">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6575,21 +6575,21 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D195">
-        <v>98</v>
+        <v>432</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6607,21 +6607,21 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D196">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6649,11 +6649,11 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D197">
-        <v>10</v>
+        <v>90</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6681,11 +6681,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D198">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6708,16 +6708,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D199">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6740,16 +6740,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D200">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6777,11 +6777,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D201">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6809,11 +6809,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6841,11 +6841,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D203">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6873,11 +6873,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D204">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6905,11 +6905,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D205">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D206">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6969,11 +6969,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D207">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -7001,11 +7001,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D208">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7033,11 +7033,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D209">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7060,16 +7060,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D210">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7092,16 +7092,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D211">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D212">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D213">
-        <v>115</v>
+        <v>34</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D214">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D215">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D216">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D217">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D218">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D219">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7417,11 +7417,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D221">
-        <v>239</v>
+        <v>22</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7449,11 +7449,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D223">
-        <v>44</v>
+        <v>239</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7513,11 +7513,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D224">
-        <v>341</v>
+        <v>1</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7545,11 +7545,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D225">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7577,11 +7577,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D226">
-        <v>55</v>
+        <v>341</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7609,11 +7609,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D227">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7641,11 +7641,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D228">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7673,11 +7673,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D229">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7705,11 +7705,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D230">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7737,11 +7737,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D231">
-        <v>291</v>
+        <v>1</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7769,11 +7769,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D232">
-        <v>73</v>
+        <v>10</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D233">
-        <v>16</v>
+        <v>261</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7828,16 +7828,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D234">
-        <v>615</v>
+        <v>73</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7860,16 +7860,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D235">
-        <v>245</v>
+        <v>16</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D236">
-        <v>107</v>
+        <v>615</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D237">
-        <v>27</v>
+        <v>245</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D238">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D239">
-        <v>607</v>
+        <v>45</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D240">
-        <v>430</v>
+        <v>136</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D241">
-        <v>22</v>
+        <v>684</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D242">
-        <v>100</v>
+        <v>534</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D243">
-        <v>618</v>
+        <v>22</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D244">
-        <v>582</v>
+        <v>100</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D245">
-        <v>464</v>
+        <v>618</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D246">
-        <v>375</v>
+        <v>604</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8249,11 +8249,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D247">
-        <v>24</v>
+        <v>464</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8281,11 +8281,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D248">
-        <v>50</v>
+        <v>375</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8313,11 +8313,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D249">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8345,11 +8345,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D250">
-        <v>197</v>
+        <v>50</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8377,11 +8377,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D251">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8409,11 +8409,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D252">
-        <v>1434</v>
+        <v>183</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8441,11 +8441,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D253">
-        <v>323</v>
+        <v>96</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8473,11 +8473,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D254">
-        <v>329</v>
+        <v>1418</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8505,11 +8505,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D255">
-        <v>980</v>
+        <v>323</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8537,11 +8537,11 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D256">
-        <v>110</v>
+        <v>329</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8569,11 +8569,11 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D257">
-        <v>79</v>
+        <v>904</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -8601,11 +8601,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D258">
-        <v>623</v>
+        <v>110</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8633,11 +8633,11 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D259">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -8665,11 +8665,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D260">
-        <v>144</v>
+        <v>623</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -8692,16 +8692,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D261">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -8724,16 +8724,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D262">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -8756,16 +8756,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D263">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -8793,11 +8793,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D264">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -8825,11 +8825,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D265">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -8857,11 +8857,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D266">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -8884,16 +8884,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D267">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8916,16 +8916,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D268">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -8953,11 +8953,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D269">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -8985,7 +8985,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D270">
@@ -9017,11 +9017,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D271">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D272">
@@ -9076,16 +9076,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D273">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -9113,11 +9113,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D274">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -9145,11 +9145,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D275">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -9172,16 +9172,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D276">
-        <v>563</v>
+        <v>46</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -9204,16 +9204,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D277">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -9241,11 +9241,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D278">
-        <v>85</v>
+        <v>617</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -9273,11 +9273,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D279">
-        <v>312</v>
+        <v>26</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -9305,11 +9305,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D280">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -9337,11 +9337,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D281">
-        <v>146</v>
+        <v>278</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -9369,11 +9369,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D282">
-        <v>62</v>
+        <v>194</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D283">
-        <v>853</v>
+        <v>148</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -9433,11 +9433,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D284">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D285">
-        <v>473</v>
+        <v>809</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D286">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -9529,11 +9529,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D287">
-        <v>706</v>
+        <v>473</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -9561,11 +9561,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D288">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -9593,11 +9593,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D289">
-        <v>98</v>
+        <v>706</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -9625,11 +9625,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D290">
-        <v>185</v>
+        <v>72</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -9657,11 +9657,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D291">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -9689,11 +9689,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D292">
-        <v>30</v>
+        <v>185</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9721,11 +9721,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D293">
-        <v>117</v>
+        <v>161</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D294">
@@ -9785,11 +9785,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D295">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -9817,11 +9817,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D296">
-        <v>334</v>
+        <v>67</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -9849,11 +9849,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D297">
-        <v>60</v>
+        <v>156</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -9881,11 +9881,11 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D298">
-        <v>172</v>
+        <v>322</v>
       </c>
       <c r="E298">
         <v>0</v>
@@ -9913,11 +9913,11 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D299">
-        <v>646</v>
+        <v>60</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -9945,11 +9945,11 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D300">
-        <v>58</v>
+        <v>172</v>
       </c>
       <c r="E300">
         <v>0</v>
@@ -9972,27 +9972,123 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="D301">
+        <v>646</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>0</v>
+      </c>
+      <c r="G301">
+        <v>0</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="D302">
+        <v>58</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>0</v>
+      </c>
+      <c r="G302">
+        <v>0</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
           <t>TCT_Pin khác</t>
         </is>
       </c>
-      <c r="C301" t="inlineStr">
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>DBN</t>
+        </is>
+      </c>
+      <c r="D303">
+        <v>70</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="D301">
+      <c r="D304">
         <v>2</v>
       </c>
-      <c r="E301">
-        <v>0</v>
-      </c>
-      <c r="F301">
-        <v>0</v>
-      </c>
-      <c r="G301">
-        <v>0</v>
-      </c>
-      <c r="H301">
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="H304">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H304"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -409,11 +409,11 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D2">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -425,7 +425,7 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>45</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -436,28 +436,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -468,28 +468,28 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D4">
         <v>20</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -500,28 +500,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -537,23 +537,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -564,28 +564,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -596,28 +596,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>332</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9">
@@ -628,28 +628,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D9">
+        <v>25</v>
+      </c>
+      <c r="E9">
         <v>2</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
       <c r="F9">
+        <v>25</v>
+      </c>
+      <c r="G9">
         <v>2</v>
       </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
       <c r="H9">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -660,28 +660,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D10">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="E10">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="G10">
         <v>1</v>
       </c>
       <c r="H10">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -692,28 +692,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
@@ -724,28 +724,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -756,28 +756,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D13">
-        <v>24</v>
+        <v>187</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -793,23 +793,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D14">
-        <v>24</v>
+        <v>316</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15">
@@ -825,11 +825,11 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -852,28 +852,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D16">
-        <v>559</v>
+        <v>140</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>71</v>
+        <v>140</v>
       </c>
       <c r="G16">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -884,28 +884,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D17">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -916,28 +916,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -948,28 +948,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>295</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F19">
-        <v>28</v>
+        <v>285</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H19">
-        <v>30</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20">
@@ -980,28 +980,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D20">
-        <v>28</v>
+        <v>253</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>28</v>
+        <v>188</v>
       </c>
     </row>
     <row r="21">
@@ -1012,28 +1012,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D21">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1044,28 +1044,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>154</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>150</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H22">
-        <v>2</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
@@ -1076,28 +1076,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D23">
-        <v>225</v>
+        <v>377</v>
       </c>
       <c r="E23">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>215</v>
+        <v>51</v>
       </c>
       <c r="G23">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H23">
-        <v>215</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24">
@@ -1108,28 +1108,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D24">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F24">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H24">
-        <v>16</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25">
@@ -1145,23 +1145,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D25">
-        <v>64</v>
+        <v>110</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F25">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="G25">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H25">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D26">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D27">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D28">
-        <v>439</v>
+        <v>218</v>
       </c>
       <c r="E28">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>375</v>
+        <v>64</v>
       </c>
       <c r="G28">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>375</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D29">
-        <v>10</v>
+        <v>723</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="F29">
-        <v>10</v>
+        <v>674</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="H29">
-        <v>10</v>
+        <v>674</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D30">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F30">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H30">
-        <v>44</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D31">
-        <v>668</v>
+        <v>283</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>197</v>
+        <v>240</v>
       </c>
       <c r="G31">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H31">
-        <v>456</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D32">
-        <v>68</v>
+        <v>431</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>68</v>
+        <v>227</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H32">
-        <v>68</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D33">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34">
@@ -1428,16 +1428,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D34">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1446,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1460,28 +1460,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D35">
-        <v>157</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1492,28 +1492,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D36">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F36">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H36">
-        <v>38</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37">
@@ -1524,28 +1524,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D37">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
@@ -1556,28 +1556,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D38">
-        <v>514</v>
+        <v>129</v>
       </c>
       <c r="E38">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>448</v>
+        <v>125</v>
       </c>
       <c r="G38">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>448</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39">
@@ -1588,28 +1588,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D39">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F39">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H39">
-        <v>12</v>
+        <v>97</v>
       </c>
     </row>
     <row r="40">
@@ -1620,28 +1620,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D40">
-        <v>1812</v>
+        <v>23</v>
       </c>
       <c r="E40">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>1500</v>
+        <v>23</v>
       </c>
       <c r="G40">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>1500</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D41">
         <v>12</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D42">
-        <v>8</v>
+        <v>295</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>8</v>
+        <v>279</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H42">
-        <v>8</v>
+        <v>279</v>
       </c>
     </row>
     <row r="43">
@@ -1716,28 +1716,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>278</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44">
@@ -1748,28 +1748,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H44">
-        <v>5</v>
+        <v>105</v>
       </c>
     </row>
     <row r="45">
@@ -1780,16 +1780,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1812,28 +1812,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D46">
-        <v>16</v>
+        <v>713</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="F46">
-        <v>16</v>
+        <v>713</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H46">
-        <v>16</v>
+        <v>713</v>
       </c>
     </row>
     <row r="47">
@@ -1844,28 +1844,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D47">
-        <v>3</v>
+        <v>924</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F47">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>377</v>
       </c>
     </row>
     <row r="48">
@@ -1876,28 +1876,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49">
@@ -1913,23 +1913,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D49">
-        <v>34</v>
+        <v>644</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F49">
-        <v>26</v>
+        <v>628</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H49">
-        <v>26</v>
+        <v>628</v>
       </c>
     </row>
     <row r="50">
@@ -1945,23 +1945,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D50">
+        <v>12</v>
+      </c>
+      <c r="E50">
         <v>1</v>
       </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
       <c r="F50">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G50">
         <v>1</v>
       </c>
       <c r="H50">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
@@ -1977,23 +1977,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D51">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E51">
         <v>1</v>
       </c>
       <c r="F51">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
@@ -2009,23 +2009,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D52">
-        <v>42</v>
+        <v>515</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F52">
-        <v>42</v>
+        <v>515</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="H52">
-        <v>42</v>
+        <v>515</v>
       </c>
     </row>
     <row r="53">
@@ -2041,23 +2041,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D53">
-        <v>647</v>
+        <v>48</v>
       </c>
       <c r="E53">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F53">
-        <v>316</v>
+        <v>16</v>
       </c>
       <c r="G53">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="H53">
-        <v>420</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54">
@@ -2073,23 +2073,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D54">
-        <v>18</v>
+        <v>1502</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="F54">
-        <v>18</v>
+        <v>1240</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="H54">
-        <v>18</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="55">
@@ -2105,23 +2105,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D55">
-        <v>693</v>
+        <v>162</v>
       </c>
       <c r="E55">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="F55">
-        <v>665</v>
+        <v>51</v>
       </c>
       <c r="G55">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>665</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56">
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="D56">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2150,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2173,19 +2173,19 @@
         </is>
       </c>
       <c r="D57">
-        <v>352</v>
+        <v>1580</v>
       </c>
       <c r="E57">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="F57">
-        <v>310</v>
+        <v>1089</v>
       </c>
       <c r="G57">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="H57">
-        <v>310</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="58">
@@ -2205,19 +2205,19 @@
         </is>
       </c>
       <c r="D58">
-        <v>197</v>
+        <v>34</v>
       </c>
       <c r="E58">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F58">
-        <v>170</v>
+        <v>10</v>
       </c>
       <c r="G58">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H58">
-        <v>170</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -2233,75 +2233,75 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D59">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F59">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H59">
-        <v>54</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D60">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H60">
-        <v>0</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D61">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2319,33 +2319,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63">
@@ -2356,16 +2356,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D63">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2388,16 +2388,16 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2420,16 +2420,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D65">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2452,16 +2452,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2521,11 +2521,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D68">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D69">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2585,11 +2585,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2617,11 +2617,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D71">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2777,11 +2777,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D76">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2804,16 +2804,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D78">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D79">
@@ -2905,11 +2905,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D80">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2937,11 +2937,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D81">
-        <v>116</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D82">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3001,11 +3001,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D83">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3065,11 +3065,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D85">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D86">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D87">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3161,11 +3161,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3225,11 +3225,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D90">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D91">
-        <v>44</v>
+        <v>2</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D92">
-        <v>4</v>
+        <v>338</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3316,16 +3316,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D93">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3348,16 +3348,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D94">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D95">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3449,11 +3449,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D97">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D98">
-        <v>133</v>
+        <v>2</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3513,11 +3513,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D99">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D100">
-        <v>174</v>
+        <v>76</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D101">
-        <v>408</v>
+        <v>1</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D102">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D103">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3673,11 +3673,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D104">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3705,11 +3705,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D105">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D106">
-        <v>490</v>
+        <v>10</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D107">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3833,11 +3833,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D109">
-        <v>252</v>
+        <v>1</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D110">
-        <v>753</v>
+        <v>7</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D111">
-        <v>1661</v>
+        <v>1</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>269</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D113">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D114">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4025,11 +4025,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D115">
-        <v>108</v>
+        <v>25</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4057,11 +4057,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D116">
-        <v>18</v>
+        <v>180</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4089,11 +4089,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D117">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4116,16 +4116,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D118">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4148,16 +4148,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D119">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D120">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D121">
@@ -4249,11 +4249,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4281,11 +4281,11 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D123">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4345,11 +4345,11 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4372,16 +4372,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Jinko 625</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4404,16 +4404,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D127">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4436,16 +4436,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jinko 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D128">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D129">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4505,11 +4505,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D131">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4569,11 +4569,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D132">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4601,11 +4601,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D133">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4628,16 +4628,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4660,16 +4660,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D135">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4697,11 +4697,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4729,11 +4729,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D137">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4756,16 +4756,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4788,12 +4788,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D139">
@@ -4820,16 +4820,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D140">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D141">
-        <v>840</v>
+        <v>92</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D142">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4921,11 +4921,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D143">
-        <v>174</v>
+        <v>48</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D144">
-        <v>63</v>
+        <v>387</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D145">
@@ -5017,11 +5017,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D146">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5049,11 +5049,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D147">
-        <v>72</v>
+        <v>138</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D148">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D149">
-        <v>296</v>
+        <v>29</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5177,11 +5177,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D151">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D152">
-        <v>141</v>
+        <v>6</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5241,11 +5241,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D154">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D155">
-        <v>22</v>
+        <v>363</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5337,11 +5337,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D156">
-        <v>144</v>
+        <v>2</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D157">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D158">
-        <v>170</v>
+        <v>6</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D159">
-        <v>186</v>
+        <v>11</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5465,11 +5465,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D160">
-        <v>19</v>
+        <v>425</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D161">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D162">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D163">
-        <v>508</v>
+        <v>67</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D164">
-        <v>119</v>
+        <v>582</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5625,11 +5625,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D165">
-        <v>436</v>
+        <v>120</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5657,11 +5657,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D166">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D167">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5721,11 +5721,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D168">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5748,16 +5748,16 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D169">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5775,21 +5775,21 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D170">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5807,21 +5807,21 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D171">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5839,21 +5839,21 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D172">
-        <v>1188</v>
+        <v>4</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5871,21 +5871,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D173">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="D174">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="D175">
-        <v>330</v>
+        <v>5</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="D176">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5999,21 +5999,21 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D177">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6031,21 +6031,21 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D178">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6063,21 +6063,21 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D179">
-        <v>2064</v>
+        <v>2</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6095,21 +6095,21 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 535</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D180">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>6409</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>649</v>
+        <v>4</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6223,21 +6223,21 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Jinko 535</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D184">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6255,21 +6255,21 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6287,21 +6287,21 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D186">
-        <v>1980</v>
+        <v>36</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6319,21 +6319,21 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Jinko 545</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D187">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="D188">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>324</v>
+        <v>19</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Jinko 545</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6461,7 +6461,7 @@
         </is>
       </c>
       <c r="D191">
-        <v>3</v>
+        <v>180</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="D192">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6511,21 +6511,21 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D193">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6543,21 +6543,21 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D194">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6575,21 +6575,21 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D195">
-        <v>432</v>
+        <v>48</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6607,21 +6607,21 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D196">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6644,16 +6644,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D197">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6676,16 +6676,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D198">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6708,16 +6708,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D199">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6740,16 +6740,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D200">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D201">
@@ -6804,16 +6804,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D202">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6836,16 +6836,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D203">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6868,16 +6868,16 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6900,16 +6900,16 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D205">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6932,16 +6932,16 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D206">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D207">
@@ -6996,16 +6996,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D208">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7028,16 +7028,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D209">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7060,16 +7060,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7092,16 +7092,16 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D211">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D212">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D213">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D214">
-        <v>7</v>
+        <v>224</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D215">
-        <v>115</v>
+        <v>18</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D216">
-        <v>53</v>
+        <v>352</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D217">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D218">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D219">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D220">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7417,11 +7417,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D221">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7449,11 +7449,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D222">
-        <v>2</v>
+        <v>337</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D223">
-        <v>239</v>
+        <v>29</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7513,11 +7513,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D224">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7540,16 +7540,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D225">
-        <v>44</v>
+        <v>494</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D226">
-        <v>341</v>
+        <v>129</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7604,16 +7604,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D227">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7636,16 +7636,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D228">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7668,16 +7668,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D229">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7700,16 +7700,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D230">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7732,16 +7732,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D231">
-        <v>1</v>
+        <v>174</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7764,16 +7764,16 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D232">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7796,16 +7796,16 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D233">
-        <v>261</v>
+        <v>89</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7828,16 +7828,16 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D234">
-        <v>73</v>
+        <v>502</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7860,16 +7860,16 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D235">
-        <v>16</v>
+        <v>186</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D236">
-        <v>615</v>
+        <v>287</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D237">
-        <v>245</v>
+        <v>129</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D238">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D239">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D240">
-        <v>136</v>
+        <v>43</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D241">
-        <v>684</v>
+        <v>111</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D242">
-        <v>534</v>
+        <v>48</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D243">
-        <v>22</v>
+        <v>772</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D244">
-        <v>100</v>
+        <v>33</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D245">
-        <v>618</v>
+        <v>30</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D246">
-        <v>604</v>
+        <v>565</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8249,11 +8249,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D247">
-        <v>464</v>
+        <v>186</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8281,11 +8281,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D248">
-        <v>375</v>
+        <v>4</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8313,11 +8313,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D249">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8345,11 +8345,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D250">
-        <v>50</v>
+        <v>442</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8377,11 +8377,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D251">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8409,11 +8409,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D252">
-        <v>183</v>
+        <v>34</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8436,16 +8436,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D253">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8468,16 +8468,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D254">
-        <v>1418</v>
+        <v>1</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8500,16 +8500,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D255">
-        <v>323</v>
+        <v>2</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8532,16 +8532,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D256">
-        <v>329</v>
+        <v>16</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -8573,7 +8573,7 @@
         </is>
       </c>
       <c r="D257">
-        <v>904</v>
+        <v>7</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -8596,16 +8596,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D258">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8628,16 +8628,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D259">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -8660,16 +8660,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D260">
-        <v>623</v>
+        <v>1</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -8692,16 +8692,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D261">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -8724,16 +8724,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D262">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -8756,16 +8756,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D263">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -8788,16 +8788,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D264">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -8820,16 +8820,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D265">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -8852,16 +8852,16 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D266">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -8884,16 +8884,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D267">
-        <v>16</v>
+        <v>952</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8916,16 +8916,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D268">
-        <v>7</v>
+        <v>585</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -8948,16 +8948,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D269">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -8980,16 +8980,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D270">
-        <v>1</v>
+        <v>778</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -9012,16 +9012,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D271">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -9044,16 +9044,16 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D272">
-        <v>1</v>
+        <v>266</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -9076,16 +9076,16 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D273">
-        <v>2</v>
+        <v>206</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -9108,16 +9108,16 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D274">
-        <v>1</v>
+        <v>872</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -9140,16 +9140,16 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D275">
-        <v>4</v>
+        <v>1474</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -9172,16 +9172,16 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D276">
-        <v>46</v>
+        <v>144</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -9204,16 +9204,16 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D277">
-        <v>24</v>
+        <v>668</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -9241,11 +9241,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D278">
-        <v>617</v>
+        <v>27</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -9273,11 +9273,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D279">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -9305,11 +9305,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D280">
-        <v>85</v>
+        <v>240</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -9337,11 +9337,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D281">
-        <v>278</v>
+        <v>54</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -9369,11 +9369,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D282">
-        <v>194</v>
+        <v>52</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D283">
-        <v>148</v>
+        <v>26</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -9433,11 +9433,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D284">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D285">
-        <v>809</v>
+        <v>420</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D286">
-        <v>18</v>
+        <v>237</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -9529,11 +9529,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D287">
-        <v>473</v>
+        <v>773</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -9561,11 +9561,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D288">
-        <v>118</v>
+        <v>317</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -9593,11 +9593,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D289">
-        <v>706</v>
+        <v>586</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -9625,11 +9625,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D290">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -9657,11 +9657,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D291">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -9689,11 +9689,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D292">
-        <v>185</v>
+        <v>415</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9721,11 +9721,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D293">
-        <v>161</v>
+        <v>384</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -9753,11 +9753,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D294">
-        <v>43</v>
+        <v>414</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -9785,11 +9785,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D295">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -9817,11 +9817,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D296">
-        <v>67</v>
+        <v>416</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -9849,11 +9849,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D297">
-        <v>156</v>
+        <v>524</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -9876,16 +9876,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D298">
-        <v>322</v>
+        <v>70</v>
       </c>
       <c r="E298">
         <v>0</v>
@@ -9908,16 +9908,16 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D299">
-        <v>60</v>
+        <v>2</v>
       </c>
       <c r="E299">
         <v>0</v>
@@ -9929,166 +9929,6 @@
         <v>0</v>
       </c>
       <c r="H299">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>TQG</t>
-        </is>
-      </c>
-      <c r="D300">
-        <v>172</v>
-      </c>
-      <c r="E300">
-        <v>0</v>
-      </c>
-      <c r="F300">
-        <v>0</v>
-      </c>
-      <c r="G300">
-        <v>0</v>
-      </c>
-      <c r="H300">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>TTH</t>
-        </is>
-      </c>
-      <c r="D301">
-        <v>646</v>
-      </c>
-      <c r="E301">
-        <v>0</v>
-      </c>
-      <c r="F301">
-        <v>0</v>
-      </c>
-      <c r="G301">
-        <v>0</v>
-      </c>
-      <c r="H301">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="D302">
-        <v>58</v>
-      </c>
-      <c r="E302">
-        <v>0</v>
-      </c>
-      <c r="F302">
-        <v>0</v>
-      </c>
-      <c r="G302">
-        <v>0</v>
-      </c>
-      <c r="H302">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>TCT_Pin khác</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>DBN</t>
-        </is>
-      </c>
-      <c r="D303">
-        <v>70</v>
-      </c>
-      <c r="E303">
-        <v>0</v>
-      </c>
-      <c r="F303">
-        <v>0</v>
-      </c>
-      <c r="G303">
-        <v>0</v>
-      </c>
-      <c r="H303">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>TCT_Pin khác</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="D304">
-        <v>2</v>
-      </c>
-      <c r="E304">
-        <v>0</v>
-      </c>
-      <c r="F304">
-        <v>0</v>
-      </c>
-      <c r="G304">
-        <v>0</v>
-      </c>
-      <c r="H304">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H297"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="D12">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -765,19 +765,19 @@
         </is>
       </c>
       <c r="D13">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -861,19 +861,19 @@
         </is>
       </c>
       <c r="D16">
-        <v>140</v>
+        <v>204</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>140</v>
+        <v>204</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H16">
-        <v>140</v>
+        <v>204</v>
       </c>
     </row>
     <row r="17">
@@ -960,16 +960,16 @@
         <v>295</v>
       </c>
       <c r="E19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="G19">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H19">
-        <v>285</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20">
@@ -1017,23 +1017,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D21">
+        <v>154</v>
+      </c>
+      <c r="E21">
         <v>10</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
       <c r="F21">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22">
@@ -1049,23 +1049,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D22">
-        <v>154</v>
+        <v>377</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F22">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H22">
-        <v>150</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23">
@@ -1081,23 +1081,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D23">
-        <v>377</v>
+        <v>106</v>
       </c>
       <c r="E23">
         <v>4</v>
       </c>
       <c r="F23">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H23">
-        <v>178</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24">
@@ -1113,23 +1113,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D24">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F24">
-        <v>92</v>
+        <v>141</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H24">
-        <v>92</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25">
@@ -1145,23 +1145,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D25">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="E25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D26">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -1209,23 +1209,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>218</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D28">
-        <v>218</v>
+        <v>707</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>64</v>
+        <v>614</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="H28">
-        <v>64</v>
+        <v>614</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D29">
-        <v>723</v>
+        <v>14</v>
       </c>
       <c r="E29">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>674</v>
+        <v>14</v>
       </c>
       <c r="G29">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="H29">
-        <v>674</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D30">
-        <v>14</v>
+        <v>283</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F30">
-        <v>14</v>
+        <v>240</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H30">
-        <v>14</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D31">
-        <v>283</v>
+        <v>431</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H31">
-        <v>240</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D32">
-        <v>431</v>
+        <v>12</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>227</v>
+        <v>12</v>
       </c>
       <c r="G32">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H32">
-        <v>277</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -1433,11 +1433,11 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D34">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1460,28 +1460,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D35">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="E35">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D36">
-        <v>123</v>
+        <v>239</v>
       </c>
       <c r="E36">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F36">
-        <v>97</v>
+        <v>239</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="H36">
-        <v>97</v>
+        <v>239</v>
       </c>
     </row>
     <row r="37">
@@ -1529,23 +1529,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D37">
-        <v>42</v>
+        <v>129</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37">
-        <v>26</v>
+        <v>125</v>
       </c>
       <c r="G37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H37">
-        <v>26</v>
+        <v>125</v>
       </c>
     </row>
     <row r="38">
@@ -1561,23 +1561,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D38">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="39">
@@ -1593,23 +1593,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D39">
-        <v>154</v>
+        <v>7</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="G39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H39">
-        <v>97</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1625,23 +1625,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D40">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G40">
         <v>2</v>
       </c>
       <c r="H40">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
@@ -1657,23 +1657,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D41">
-        <v>12</v>
+        <v>295</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F41">
-        <v>12</v>
+        <v>279</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H41">
-        <v>12</v>
+        <v>279</v>
       </c>
     </row>
     <row r="42">
@@ -1689,23 +1689,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D42">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="E42">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F42">
-        <v>279</v>
+        <v>202</v>
       </c>
       <c r="G42">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H42">
-        <v>279</v>
+        <v>202</v>
       </c>
     </row>
     <row r="43">
@@ -1721,23 +1721,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D43">
-        <v>278</v>
+        <v>112</v>
       </c>
       <c r="E43">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F43">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="G43">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H43">
-        <v>224</v>
+        <v>112</v>
       </c>
     </row>
     <row r="44">
@@ -1753,23 +1753,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D44">
-        <v>105</v>
+        <v>10</v>
       </c>
       <c r="E44">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1785,23 +1785,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>701</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>701</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>701</v>
       </c>
     </row>
     <row r="46">
@@ -1817,23 +1817,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D46">
-        <v>713</v>
+        <v>924</v>
       </c>
       <c r="E46">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F46">
-        <v>713</v>
+        <v>310</v>
       </c>
       <c r="G46">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H46">
-        <v>713</v>
+        <v>377</v>
       </c>
     </row>
     <row r="47">
@@ -1849,23 +1849,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D47">
-        <v>924</v>
+        <v>301</v>
       </c>
       <c r="E47">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F47">
-        <v>310</v>
+        <v>203</v>
       </c>
       <c r="G47">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H47">
-        <v>377</v>
+        <v>217</v>
       </c>
     </row>
     <row r="48">
@@ -1881,23 +1881,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D48">
-        <v>301</v>
+        <v>654</v>
       </c>
       <c r="E48">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="F48">
-        <v>203</v>
+        <v>628</v>
       </c>
       <c r="G48">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="H48">
-        <v>217</v>
+        <v>628</v>
       </c>
     </row>
     <row r="49">
@@ -1913,23 +1913,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D49">
-        <v>644</v>
+        <v>12</v>
       </c>
       <c r="E49">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>628</v>
+        <v>12</v>
       </c>
       <c r="G49">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>628</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D50">
@@ -1977,23 +1977,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D51">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="F51">
-        <v>12</v>
+        <v>575</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="H51">
-        <v>12</v>
+        <v>575</v>
       </c>
     </row>
     <row r="52">
@@ -2009,23 +2009,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D52">
-        <v>515</v>
+        <v>34</v>
       </c>
       <c r="E52">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="F52">
-        <v>515</v>
+        <v>34</v>
       </c>
       <c r="G52">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>515</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53">
@@ -2041,23 +2041,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D53">
-        <v>48</v>
+        <v>1479</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="F53">
-        <v>16</v>
+        <v>1256</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="H53">
-        <v>16</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="54">
@@ -2073,23 +2073,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D54">
-        <v>1502</v>
+        <v>51</v>
       </c>
       <c r="E54">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>1240</v>
+        <v>51</v>
       </c>
       <c r="G54">
-        <v>54</v>
+        <v>1</v>
       </c>
       <c r="H54">
-        <v>1240</v>
+        <v>51</v>
       </c>
     </row>
     <row r="55">
@@ -2105,23 +2105,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D55">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2137,23 +2137,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D56">
-        <v>14</v>
+        <v>1678</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>1187</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="57">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D57">
-        <v>1580</v>
+        <v>34</v>
       </c>
       <c r="E57">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>1089</v>
+        <v>10</v>
       </c>
       <c r="G57">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="H57">
-        <v>1119</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58">
@@ -2201,23 +2201,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D58">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="G58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H58">
-        <v>10</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59">
@@ -2233,23 +2233,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D59">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F59">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H59">
-        <v>28</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60">
@@ -2265,23 +2265,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D60">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="E60">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="G60">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H60">
-        <v>104</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61">
@@ -2297,11 +2297,11 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D61">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2319,33 +2319,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D62">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -2361,11 +2361,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D63">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D64">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2425,11 +2425,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D65">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2452,16 +2452,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D67">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2521,11 +2521,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D69">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2585,11 +2585,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2617,11 +2617,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D72">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D73">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D76">
@@ -2809,11 +2809,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D78">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D80">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2937,11 +2937,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3001,11 +3001,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D83">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D84">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3065,11 +3065,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D85">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D86">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3161,11 +3161,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D89">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3225,11 +3225,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D90">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D92">
-        <v>338</v>
+        <v>7</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D93">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3348,16 +3348,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D94">
-        <v>38</v>
+        <v>107</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D95">
-        <v>61</v>
+        <v>4</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D96">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3449,11 +3449,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3513,11 +3513,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D99">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D100">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D103">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3673,11 +3673,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D104">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3705,11 +3705,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D105">
-        <v>29</v>
+        <v>253</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D106">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D107">
-        <v>312</v>
+        <v>1</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D108">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D109">
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D110">
-        <v>7</v>
+        <v>269</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D112">
-        <v>269</v>
+        <v>35</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D113">
-        <v>49</v>
+        <v>324</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D114">
-        <v>324</v>
+        <v>25</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4025,11 +4025,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D115">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4057,11 +4057,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D116">
-        <v>180</v>
+        <v>10</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4084,16 +4084,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D117">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4121,11 +4121,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4153,11 +4153,11 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D119">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4185,11 +4185,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4217,11 +4217,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D121">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4249,11 +4249,11 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4281,7 +4281,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D123">
@@ -4313,11 +4313,11 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4340,16 +4340,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Jinko 625</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D125">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4372,16 +4372,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jinko 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D126">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4409,11 +4409,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D127">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4441,11 +4441,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D129">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4505,11 +4505,11 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D130">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4537,11 +4537,11 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D131">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4569,11 +4569,11 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4596,16 +4596,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D133">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4633,11 +4633,11 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D134">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4665,11 +4665,11 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D135">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4697,11 +4697,11 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4724,16 +4724,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D137">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4761,11 +4761,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D138">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4793,11 +4793,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4825,11 +4825,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D140">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D141">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D142">
-        <v>250</v>
+        <v>48</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4921,11 +4921,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D143">
-        <v>48</v>
+        <v>359</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D144">
-        <v>387</v>
+        <v>3</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4985,11 +4985,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5017,11 +5017,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5049,11 +5049,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D147">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D148">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D149">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5145,7 +5145,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D150">
@@ -5177,11 +5177,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D152">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5241,11 +5241,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D153">
-        <v>160</v>
+        <v>248</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D154">
-        <v>248</v>
+        <v>335</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D155">
-        <v>363</v>
+        <v>2</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5337,11 +5337,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D157">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D158">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D159">
-        <v>11</v>
+        <v>425</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5465,11 +5465,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D160">
-        <v>425</v>
+        <v>71</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D161">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D162">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D163">
-        <v>67</v>
+        <v>582</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D164">
-        <v>582</v>
+        <v>40</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5625,11 +5625,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D165">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5657,11 +5657,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D166">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D167">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5716,16 +5716,16 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D168">
-        <v>103</v>
+        <v>1</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5743,21 +5743,21 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="D170">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5885,7 +5885,7 @@
         </is>
       </c>
       <c r="D173">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="D175">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5967,21 +5967,21 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D176">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 535</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="D179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jinko 535</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -6109,7 +6109,7 @@
         </is>
       </c>
       <c r="D180">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -6141,7 +6141,7 @@
         </is>
       </c>
       <c r="D181">
-        <v>1</v>
+        <v>5617</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6164,7 +6164,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -6173,7 +6173,7 @@
         </is>
       </c>
       <c r="D182">
-        <v>6409</v>
+        <v>4</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6191,21 +6191,21 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D183">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6237,7 +6237,7 @@
         </is>
       </c>
       <c r="D184">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 545</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Jinko 545</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="D188">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="D189">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="D190">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6447,21 +6447,21 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D191">
-        <v>180</v>
+        <v>52</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6479,21 +6479,21 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D192">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6521,11 +6521,11 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D193">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6548,16 +6548,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D194">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6580,16 +6580,16 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D195">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6617,11 +6617,11 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D196">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D197">
@@ -6681,11 +6681,11 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D198">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6713,11 +6713,11 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D199">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6740,16 +6740,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D200">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6772,16 +6772,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D201">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6809,11 +6809,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D202">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6841,11 +6841,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D203">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6873,11 +6873,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D204">
-        <v>99</v>
+        <v>14</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6905,11 +6905,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D205">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D206">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6969,11 +6969,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D207">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -7001,11 +7001,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D208">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7033,11 +7033,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D209">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7065,7 +7065,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D210">
@@ -7097,11 +7097,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D211">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D212">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D213">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D214">
-        <v>224</v>
+        <v>314</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D215">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D216">
-        <v>352</v>
+        <v>10</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D217">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D218">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D219">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D220">
-        <v>2</v>
+        <v>337</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7417,11 +7417,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D221">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7449,11 +7449,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D222">
-        <v>337</v>
+        <v>16</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7476,16 +7476,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D223">
-        <v>29</v>
+        <v>466</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7508,16 +7508,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D224">
-        <v>16</v>
+        <v>129</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7545,11 +7545,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D225">
-        <v>494</v>
+        <v>52</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7577,11 +7577,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D226">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7609,11 +7609,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D227">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7641,11 +7641,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D228">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7673,11 +7673,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D229">
-        <v>25</v>
+        <v>174</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7705,11 +7705,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D230">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7737,11 +7737,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D231">
-        <v>174</v>
+        <v>59</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7769,11 +7769,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D232">
-        <v>7</v>
+        <v>502</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D233">
-        <v>89</v>
+        <v>186</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7833,11 +7833,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D234">
-        <v>502</v>
+        <v>287</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7865,11 +7865,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D235">
-        <v>186</v>
+        <v>237</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D236">
-        <v>287</v>
+        <v>59</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D237">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D238">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D239">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D240">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D241">
-        <v>111</v>
+        <v>738</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D242">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D243">
-        <v>772</v>
+        <v>30</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D244">
-        <v>33</v>
+        <v>565</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D245">
-        <v>30</v>
+        <v>186</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D246">
-        <v>565</v>
+        <v>4</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8249,11 +8249,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D247">
-        <v>186</v>
+        <v>14</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8281,11 +8281,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D248">
-        <v>4</v>
+        <v>395</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8313,11 +8313,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D249">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8345,11 +8345,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D250">
-        <v>442</v>
+        <v>34</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8372,16 +8372,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D251">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8404,16 +8404,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D252">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8441,11 +8441,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8473,11 +8473,11 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8505,11 +8505,11 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D255">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8532,16 +8532,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D256">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8564,16 +8564,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D257">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -8601,11 +8601,11 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D259">
@@ -8665,11 +8665,11 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D261">
@@ -8724,16 +8724,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D262">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -8761,11 +8761,11 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D263">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -8793,11 +8793,11 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D264">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -8820,16 +8820,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D265">
-        <v>46</v>
+        <v>961</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -8852,16 +8852,16 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D266">
-        <v>24</v>
+        <v>346</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -8889,11 +8889,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D267">
-        <v>952</v>
+        <v>86</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8921,11 +8921,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D268">
-        <v>585</v>
+        <v>768</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -8953,11 +8953,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D269">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -8985,11 +8985,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D270">
-        <v>778</v>
+        <v>232</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -9017,11 +9017,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D271">
-        <v>83</v>
+        <v>206</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -9049,11 +9049,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D272">
-        <v>266</v>
+        <v>869</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -9081,11 +9081,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D273">
-        <v>206</v>
+        <v>1426</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -9113,11 +9113,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D274">
-        <v>872</v>
+        <v>136</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -9145,11 +9145,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D275">
-        <v>1474</v>
+        <v>656</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -9177,11 +9177,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D276">
-        <v>144</v>
+        <v>27</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -9209,11 +9209,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D277">
-        <v>668</v>
+        <v>151</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -9241,11 +9241,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D278">
-        <v>27</v>
+        <v>240</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -9273,11 +9273,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D279">
-        <v>151</v>
+        <v>54</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -9305,11 +9305,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D280">
-        <v>240</v>
+        <v>52</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -9337,11 +9337,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D281">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -9369,11 +9369,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D282">
-        <v>52</v>
+        <v>111</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D283">
-        <v>26</v>
+        <v>420</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -9433,11 +9433,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D284">
-        <v>111</v>
+        <v>167</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D285">
-        <v>420</v>
+        <v>713</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D286">
-        <v>237</v>
+        <v>275</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -9529,11 +9529,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D287">
-        <v>773</v>
+        <v>586</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -9561,11 +9561,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D288">
-        <v>317</v>
+        <v>156</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -9593,11 +9593,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D289">
-        <v>586</v>
+        <v>117</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -9625,11 +9625,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D290">
-        <v>156</v>
+        <v>342</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -9657,11 +9657,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D291">
-        <v>117</v>
+        <v>390</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -9689,11 +9689,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D292">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9721,11 +9721,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D293">
-        <v>384</v>
+        <v>91</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -9753,11 +9753,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D294">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -9785,11 +9785,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D295">
-        <v>91</v>
+        <v>516</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -9812,16 +9812,16 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D296">
-        <v>416</v>
+        <v>70</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -9844,16 +9844,16 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D297">
-        <v>524</v>
+        <v>2</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -9865,70 +9865,6 @@
         <v>0</v>
       </c>
       <c r="H297">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>TCT_Pin khác</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>DBN</t>
-        </is>
-      </c>
-      <c r="D298">
-        <v>70</v>
-      </c>
-      <c r="E298">
-        <v>0</v>
-      </c>
-      <c r="F298">
-        <v>0</v>
-      </c>
-      <c r="G298">
-        <v>0</v>
-      </c>
-      <c r="H298">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>TCT_Pin khác</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="D299">
-        <v>2</v>
-      </c>
-      <c r="E299">
-        <v>0</v>
-      </c>
-      <c r="F299">
-        <v>0</v>
-      </c>
-      <c r="G299">
-        <v>0</v>
-      </c>
-      <c r="H299">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H297"/>
+  <dimension ref="A1:H293"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -605,19 +605,19 @@
         </is>
       </c>
       <c r="D8">
-        <v>332</v>
+        <v>395</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>14</v>
+        <v>152</v>
       </c>
       <c r="G8">
         <v>8</v>
       </c>
       <c r="H8">
-        <v>86</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
@@ -733,19 +733,19 @@
         </is>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>271</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H12">
-        <v>28</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
@@ -761,23 +761,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D13">
-        <v>173</v>
+        <v>16</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>166</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -793,23 +793,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D14">
-        <v>316</v>
+        <v>197</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14">
-        <v>242</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15">
@@ -825,23 +825,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D15">
-        <v>32</v>
+        <v>302</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
@@ -852,28 +852,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D16">
-        <v>204</v>
+        <v>32</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="G16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -889,23 +889,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>282</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H17">
-        <v>1</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18">
@@ -921,23 +921,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D18">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -953,23 +953,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D19">
-        <v>295</v>
+        <v>14</v>
       </c>
       <c r="E19">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>271</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>271</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20">
@@ -985,23 +985,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D20">
-        <v>253</v>
+        <v>285</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F20">
-        <v>188</v>
+        <v>271</v>
       </c>
       <c r="G20">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H20">
-        <v>188</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21">
@@ -1017,23 +1017,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D21">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F21">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H21">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
@@ -1049,23 +1049,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D22">
-        <v>377</v>
+        <v>168</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F22">
-        <v>51</v>
+        <v>144</v>
       </c>
       <c r="G22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H22">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23">
@@ -1081,23 +1081,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D23">
-        <v>106</v>
+        <v>377</v>
       </c>
       <c r="E23">
         <v>4</v>
       </c>
       <c r="F23">
-        <v>92</v>
+        <v>51</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H23">
-        <v>92</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24">
@@ -1113,23 +1113,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D24">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F24">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="G24">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H24">
-        <v>141</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25">
@@ -1145,23 +1145,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D25">
-        <v>32</v>
+        <v>143</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1209,23 +1209,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D27">
-        <v>218</v>
+        <v>10</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F27">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>64</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D28">
-        <v>707</v>
+        <v>218</v>
       </c>
       <c r="E28">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F28">
-        <v>614</v>
+        <v>64</v>
       </c>
       <c r="G28">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H28">
-        <v>614</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D29">
-        <v>14</v>
+        <v>938</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="F29">
-        <v>14</v>
+        <v>697</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="H29">
-        <v>14</v>
+        <v>697</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D30">
-        <v>283</v>
+        <v>41</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>240</v>
+        <v>37</v>
       </c>
       <c r="G30">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>240</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D31">
-        <v>431</v>
+        <v>283</v>
       </c>
       <c r="E31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="G31">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H31">
-        <v>277</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D32">
-        <v>12</v>
+        <v>333</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>12</v>
+        <v>227</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H32">
-        <v>12</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D33">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -1428,28 +1428,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35">
@@ -1460,28 +1460,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D35">
-        <v>82</v>
+        <v>2</v>
       </c>
       <c r="E35">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G35">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H35">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1492,28 +1492,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D36">
-        <v>239</v>
+        <v>45</v>
       </c>
       <c r="E36">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F36">
-        <v>239</v>
+        <v>45</v>
       </c>
       <c r="G36">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>239</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -1529,23 +1529,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D37">
-        <v>129</v>
+        <v>501</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="F37">
-        <v>125</v>
+        <v>475</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H37">
-        <v>125</v>
+        <v>487</v>
       </c>
     </row>
     <row r="38">
@@ -1561,23 +1561,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D38">
-        <v>148</v>
+        <v>443</v>
       </c>
       <c r="E38">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F38">
-        <v>91</v>
+        <v>443</v>
       </c>
       <c r="G38">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="H38">
-        <v>91</v>
+        <v>443</v>
       </c>
     </row>
     <row r="39">
@@ -1593,23 +1593,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D39">
-        <v>7</v>
+        <v>129</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F39">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H39">
-        <v>7</v>
+        <v>125</v>
       </c>
     </row>
     <row r="40">
@@ -1625,23 +1625,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D40">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F40">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="G40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H40">
-        <v>19</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41">
@@ -1657,23 +1657,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D41">
-        <v>295</v>
+        <v>61</v>
       </c>
       <c r="E41">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F41">
-        <v>279</v>
+        <v>61</v>
       </c>
       <c r="G41">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="H41">
-        <v>279</v>
+        <v>61</v>
       </c>
     </row>
     <row r="42">
@@ -1689,23 +1689,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D42">
-        <v>256</v>
+        <v>12</v>
       </c>
       <c r="E42">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>202</v>
+        <v>12</v>
       </c>
       <c r="G42">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H42">
-        <v>202</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -1721,23 +1721,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D43">
-        <v>112</v>
+        <v>295</v>
       </c>
       <c r="E43">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F43">
-        <v>112</v>
+        <v>279</v>
       </c>
       <c r="G43">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H43">
-        <v>112</v>
+        <v>279</v>
       </c>
     </row>
     <row r="44">
@@ -1753,23 +1753,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>248</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>194</v>
       </c>
     </row>
     <row r="45">
@@ -1785,23 +1785,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D45">
-        <v>701</v>
+        <v>115</v>
       </c>
       <c r="E45">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="F45">
-        <v>701</v>
+        <v>115</v>
       </c>
       <c r="G45">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H45">
-        <v>701</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46">
@@ -1817,23 +1817,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D46">
-        <v>924</v>
+        <v>691</v>
       </c>
       <c r="E46">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F46">
-        <v>310</v>
+        <v>691</v>
       </c>
       <c r="G46">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H46">
-        <v>377</v>
+        <v>691</v>
       </c>
     </row>
     <row r="47">
@@ -1849,23 +1849,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D47">
-        <v>301</v>
+        <v>684</v>
       </c>
       <c r="E47">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F47">
-        <v>203</v>
+        <v>92</v>
       </c>
       <c r="G47">
         <v>13</v>
       </c>
       <c r="H47">
-        <v>217</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48">
@@ -1881,23 +1881,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D48">
-        <v>654</v>
+        <v>291</v>
       </c>
       <c r="E48">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="F48">
-        <v>628</v>
+        <v>193</v>
       </c>
       <c r="G48">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="H48">
-        <v>628</v>
+        <v>207</v>
       </c>
     </row>
     <row r="49">
@@ -1913,23 +1913,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D49">
-        <v>12</v>
+        <v>724</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F49">
-        <v>12</v>
+        <v>708</v>
       </c>
       <c r="G49">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H49">
-        <v>12</v>
+        <v>708</v>
       </c>
     </row>
     <row r="50">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D50">
@@ -1977,23 +1977,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D51">
-        <v>575</v>
+        <v>62</v>
       </c>
       <c r="E51">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>575</v>
+        <v>62</v>
       </c>
       <c r="G51">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H51">
-        <v>575</v>
+        <v>62</v>
       </c>
     </row>
     <row r="52">
@@ -2009,23 +2009,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D52">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H52">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
@@ -2041,23 +2041,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D53">
-        <v>1479</v>
+        <v>714</v>
       </c>
       <c r="E53">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F53">
-        <v>1256</v>
+        <v>682</v>
       </c>
       <c r="G53">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H53">
-        <v>1256</v>
+        <v>682</v>
       </c>
     </row>
     <row r="54">
@@ -2073,23 +2073,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D54">
-        <v>51</v>
+        <v>665</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="F54">
-        <v>51</v>
+        <v>665</v>
       </c>
       <c r="G54">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="H54">
-        <v>51</v>
+        <v>665</v>
       </c>
     </row>
     <row r="55">
@@ -2105,23 +2105,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D55">
-        <v>14</v>
+        <v>1503</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>1257</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="56">
@@ -2137,23 +2137,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D56">
-        <v>1678</v>
+        <v>51</v>
       </c>
       <c r="E56">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>1187</v>
+        <v>51</v>
       </c>
       <c r="G56">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="H56">
-        <v>1217</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D57">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F57">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -2201,23 +2201,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D58">
-        <v>42</v>
+        <v>1667</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="F58">
-        <v>28</v>
+        <v>1158</v>
       </c>
       <c r="G58">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="H58">
-        <v>28</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="59">
@@ -2233,23 +2233,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D59">
-        <v>104</v>
+        <v>34</v>
       </c>
       <c r="E59">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>104</v>
+        <v>10</v>
       </c>
       <c r="G59">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>104</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
@@ -2265,23 +2265,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D60">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="E60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F60">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="G60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H60">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61">
@@ -2297,55 +2297,55 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D61">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="G61">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H61">
-        <v>0</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D62">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
@@ -2361,11 +2361,11 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D63">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2393,11 +2393,11 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D64">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2425,11 +2425,11 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2452,16 +2452,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D66">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2489,11 +2489,11 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2521,11 +2521,11 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D68">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2553,11 +2553,11 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2585,11 +2585,11 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2617,11 +2617,11 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D71">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2649,11 +2649,11 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D72">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D74">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D76">
@@ -2809,11 +2809,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D77">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2873,11 +2873,11 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D79">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2937,11 +2937,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D81">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D82">
-        <v>80</v>
+        <v>921</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3001,11 +3001,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D83">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D84">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3065,11 +3065,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D85">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3161,11 +3161,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D88">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D89">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="D94">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3485,7 +3485,7 @@
         </is>
       </c>
       <c r="D98">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D101">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D102">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D103">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3673,11 +3673,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D104">
-        <v>10</v>
+        <v>253</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3705,11 +3705,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D105">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D106">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D108">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3833,11 +3833,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>269</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D110">
-        <v>269</v>
+        <v>49</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D111">
-        <v>49</v>
+        <v>324</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D112">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D113">
-        <v>324</v>
+        <v>134</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3988,16 +3988,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D114">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4020,16 +4020,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D115">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4052,16 +4052,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D116">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4089,11 +4089,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4121,11 +4121,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D118">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D119">
@@ -4185,11 +4185,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4217,11 +4217,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D121">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4244,16 +4244,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Jinko 625</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4276,16 +4276,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4308,16 +4308,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4340,16 +4340,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jinko 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D125">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4377,11 +4377,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D126">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4409,11 +4409,11 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4441,11 +4441,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D128">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D129">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4500,16 +4500,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D130">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4532,16 +4532,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4564,16 +4564,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D132">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D133">
@@ -4628,16 +4628,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D134">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4660,12 +4660,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D135">
@@ -4692,16 +4692,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D136">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4729,11 +4729,11 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D137">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4761,11 +4761,11 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4793,11 +4793,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D139">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4825,11 +4825,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D140">
-        <v>92</v>
+        <v>359</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D141">
-        <v>205</v>
+        <v>391</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D142">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4921,11 +4921,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D143">
-        <v>359</v>
+        <v>72</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D144">
-        <v>3</v>
+        <v>123</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4985,11 +4985,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D145">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5017,11 +5017,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D146">
-        <v>138</v>
+        <v>206</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5049,11 +5049,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D147">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D148">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D149">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D150">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5177,11 +5177,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D151">
-        <v>6</v>
+        <v>248</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D152">
-        <v>158</v>
+        <v>303</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5241,11 +5241,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D153">
-        <v>248</v>
+        <v>2</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D154">
-        <v>335</v>
+        <v>744</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D155">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5337,11 +5337,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D156">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D157">
-        <v>6</v>
+        <v>348</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D158">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D159">
-        <v>425</v>
+        <v>32</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5465,11 +5465,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D160">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D161">
-        <v>32</v>
+        <v>582</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D162">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D163">
-        <v>582</v>
+        <v>19</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D164">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5620,16 +5620,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D165">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5647,21 +5647,21 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D166">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5679,21 +5679,21 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D167">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5711,21 +5711,21 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="D169">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -5789,7 +5789,7 @@
         </is>
       </c>
       <c r="D170">
-        <v>56</v>
+        <v>5</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="D172">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5871,21 +5871,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D173">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5903,21 +5903,21 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D174">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5935,21 +5935,21 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D175">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Jinko 535</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>5005</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Jinko 535</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="D179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6095,21 +6095,21 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6127,21 +6127,21 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D181">
-        <v>5617</v>
+        <v>24</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6159,21 +6159,21 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D182">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6196,7 +6196,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Jinko 545</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -6205,7 +6205,7 @@
         </is>
       </c>
       <c r="D183">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6237,7 +6237,7 @@
         </is>
       </c>
       <c r="D184">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Jinko 545</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6351,21 +6351,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D188">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6383,21 +6383,21 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D189">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6415,21 +6415,21 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D190">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6452,16 +6452,16 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D191">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6484,16 +6484,16 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D192">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6516,16 +6516,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D193">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6553,11 +6553,11 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D194">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6585,11 +6585,11 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D195">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6617,7 +6617,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D196">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D197">
@@ -6676,16 +6676,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D198">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6708,16 +6708,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D199">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6745,11 +6745,11 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D200">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6777,11 +6777,11 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D201">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6809,11 +6809,11 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D202">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6841,11 +6841,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D203">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6873,11 +6873,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D204">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6905,11 +6905,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D205">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D206">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6969,11 +6969,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D207">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -7001,11 +7001,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D208">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7033,11 +7033,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D209">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7065,11 +7065,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D210">
-        <v>22</v>
+        <v>290</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7097,11 +7097,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D211">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D212">
-        <v>210</v>
+        <v>10</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D213">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D214">
-        <v>314</v>
+        <v>2</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D215">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D216">
-        <v>10</v>
+        <v>385</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D217">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D218">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7348,16 +7348,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D219">
-        <v>6</v>
+        <v>352</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7380,16 +7380,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D220">
-        <v>337</v>
+        <v>129</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7412,16 +7412,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D221">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7444,16 +7444,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D222">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D223">
-        <v>466</v>
+        <v>25</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7513,11 +7513,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D224">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7545,11 +7545,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D225">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7577,11 +7577,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D226">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7609,11 +7609,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D227">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7641,11 +7641,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D228">
-        <v>85</v>
+        <v>488</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7673,11 +7673,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D229">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7705,11 +7705,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D230">
-        <v>7</v>
+        <v>287</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7737,11 +7737,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D231">
-        <v>59</v>
+        <v>281</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7769,11 +7769,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D232">
-        <v>502</v>
+        <v>91</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D233">
-        <v>186</v>
+        <v>23</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7833,11 +7833,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D234">
-        <v>287</v>
+        <v>43</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7865,11 +7865,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D235">
-        <v>237</v>
+        <v>101</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D236">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D237">
-        <v>23</v>
+        <v>393</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D238">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D239">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D240">
-        <v>48</v>
+        <v>541</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D241">
-        <v>738</v>
+        <v>186</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D242">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D243">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D244">
-        <v>565</v>
+        <v>379</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D245">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D246">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8244,16 +8244,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D247">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8276,16 +8276,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D248">
-        <v>395</v>
+        <v>1</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8308,16 +8308,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D249">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8340,16 +8340,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D250">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8377,11 +8377,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8404,16 +8404,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8436,16 +8436,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D253">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8468,16 +8468,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D254">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8500,16 +8500,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D255">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8537,7 +8537,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D256">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D257">
@@ -8596,16 +8596,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D259">
@@ -8660,16 +8660,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D260">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -8692,16 +8692,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D261">
-        <v>1</v>
+        <v>494</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -8724,16 +8724,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D262">
-        <v>4</v>
+        <v>166</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -8756,16 +8756,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D263">
-        <v>46</v>
+        <v>146</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -8788,16 +8788,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D264">
-        <v>24</v>
+        <v>746</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -8825,11 +8825,11 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D265">
-        <v>961</v>
+        <v>95</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -8857,11 +8857,11 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D266">
-        <v>346</v>
+        <v>226</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -8889,11 +8889,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D267">
-        <v>86</v>
+        <v>206</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8921,11 +8921,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D268">
-        <v>768</v>
+        <v>885</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -8953,11 +8953,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D269">
-        <v>95</v>
+        <v>1354</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -8985,11 +8985,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D270">
-        <v>232</v>
+        <v>146</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -9017,11 +9017,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D271">
-        <v>206</v>
+        <v>764</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -9049,11 +9049,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D272">
-        <v>869</v>
+        <v>27</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -9081,11 +9081,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D273">
-        <v>1426</v>
+        <v>187</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -9113,11 +9113,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D274">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -9145,11 +9145,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D275">
-        <v>656</v>
+        <v>46</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -9177,11 +9177,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D276">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -9209,11 +9209,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D277">
-        <v>151</v>
+        <v>26</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -9241,11 +9241,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D278">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -9273,11 +9273,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D279">
-        <v>54</v>
+        <v>274</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -9305,11 +9305,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D280">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -9337,11 +9337,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D281">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -9369,11 +9369,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D282">
-        <v>111</v>
+        <v>261</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D283">
-        <v>420</v>
+        <v>586</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -9433,11 +9433,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D284">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D285">
-        <v>713</v>
+        <v>117</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D286">
-        <v>275</v>
+        <v>323</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -9529,11 +9529,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D287">
-        <v>586</v>
+        <v>437</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -9561,11 +9561,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D288">
-        <v>156</v>
+        <v>479</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -9593,11 +9593,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D289">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -9625,11 +9625,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D290">
-        <v>342</v>
+        <v>382</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -9657,11 +9657,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D291">
-        <v>390</v>
+        <v>659</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -9684,16 +9684,16 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D292">
-        <v>436</v>
+        <v>70</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9716,16 +9716,16 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D293">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -9737,134 +9737,6 @@
         <v>0</v>
       </c>
       <c r="H293">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>TTH</t>
-        </is>
-      </c>
-      <c r="D294">
-        <v>388</v>
-      </c>
-      <c r="E294">
-        <v>0</v>
-      </c>
-      <c r="F294">
-        <v>0</v>
-      </c>
-      <c r="G294">
-        <v>0</v>
-      </c>
-      <c r="H294">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="D295">
-        <v>516</v>
-      </c>
-      <c r="E295">
-        <v>0</v>
-      </c>
-      <c r="F295">
-        <v>0</v>
-      </c>
-      <c r="G295">
-        <v>0</v>
-      </c>
-      <c r="H295">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>TCT_Pin khác</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>DBN</t>
-        </is>
-      </c>
-      <c r="D296">
-        <v>70</v>
-      </c>
-      <c r="E296">
-        <v>0</v>
-      </c>
-      <c r="F296">
-        <v>0</v>
-      </c>
-      <c r="G296">
-        <v>0</v>
-      </c>
-      <c r="H296">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>TCT_Pin khác</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="D297">
-        <v>2</v>
-      </c>
-      <c r="E297">
-        <v>0</v>
-      </c>
-      <c r="F297">
-        <v>0</v>
-      </c>
-      <c r="G297">
-        <v>0</v>
-      </c>
-      <c r="H297">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:H299"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -601,23 +601,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D8">
-        <v>395</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="G8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>224</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -633,23 +633,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D9">
-        <v>25</v>
+        <v>243</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H9">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -665,23 +665,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D10">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>28</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -729,23 +729,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D12">
-        <v>271</v>
+        <v>28</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>111</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -761,23 +761,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D13">
-        <v>16</v>
+        <v>271</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F13">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H13">
-        <v>16</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -793,23 +793,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D14">
-        <v>197</v>
+        <v>16</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F14">
-        <v>190</v>
+        <v>16</v>
       </c>
       <c r="G14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>190</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -825,23 +825,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D15">
-        <v>302</v>
+        <v>197</v>
       </c>
       <c r="E15">
         <v>5</v>
       </c>
       <c r="F15">
-        <v>242</v>
+        <v>164</v>
       </c>
       <c r="G15">
         <v>5</v>
       </c>
       <c r="H15">
-        <v>242</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16">
@@ -857,23 +857,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D16">
-        <v>32</v>
+        <v>302</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17">
@@ -884,28 +884,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D17">
-        <v>318</v>
+        <v>56</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>282</v>
+        <v>24</v>
       </c>
       <c r="G17">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>282</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -916,28 +916,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G18">
         <v>1</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -953,23 +953,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D19">
-        <v>14</v>
+        <v>244</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>244</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H19">
-        <v>14</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20">
@@ -985,23 +985,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D20">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="E20">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F20">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="G20">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>271</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1017,23 +1017,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D21">
-        <v>223</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>158</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H21">
-        <v>158</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1049,23 +1049,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D22">
-        <v>168</v>
+        <v>14</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>144</v>
+        <v>14</v>
       </c>
       <c r="G22">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>144</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
@@ -1081,23 +1081,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D23">
-        <v>377</v>
+        <v>287</v>
       </c>
       <c r="E23">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F23">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="G23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23">
-        <v>178</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24">
@@ -1113,23 +1113,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D24">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F24">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="G24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H24">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25">
@@ -1145,23 +1145,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D25">
-        <v>143</v>
+        <v>13</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H25">
-        <v>141</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D26">
-        <v>32</v>
+        <v>168</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27">
@@ -1209,23 +1209,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>362</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H27">
-        <v>10</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D28">
-        <v>218</v>
+        <v>92</v>
       </c>
       <c r="E28">
         <v>4</v>
       </c>
       <c r="F28">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="G28">
         <v>4</v>
       </c>
       <c r="H28">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D29">
-        <v>938</v>
+        <v>96</v>
       </c>
       <c r="E29">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>697</v>
+        <v>86</v>
       </c>
       <c r="G29">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H29">
-        <v>697</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D30">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D31">
-        <v>283</v>
+        <v>10</v>
       </c>
       <c r="E31">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>240</v>
+        <v>10</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H31">
-        <v>240</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D32">
-        <v>333</v>
+        <v>218</v>
       </c>
       <c r="E32">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F32">
-        <v>227</v>
+        <v>34</v>
       </c>
       <c r="G32">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H32">
-        <v>227</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D33">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="34">
@@ -1433,23 +1433,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D34">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F34">
-        <v>38</v>
+        <v>723</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="H34">
-        <v>38</v>
+        <v>723</v>
       </c>
     </row>
     <row r="35">
@@ -1460,28 +1460,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D35">
+        <v>16</v>
+      </c>
+      <c r="E35">
         <v>2</v>
       </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
       <c r="F35">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36">
@@ -1492,28 +1492,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D36">
-        <v>45</v>
+        <v>283</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F36">
-        <v>45</v>
+        <v>240</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H36">
-        <v>45</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37">
@@ -1524,28 +1524,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D37">
-        <v>501</v>
+        <v>333</v>
       </c>
       <c r="E37">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="F37">
-        <v>475</v>
+        <v>227</v>
       </c>
       <c r="G37">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="H37">
-        <v>487</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38">
@@ -1556,28 +1556,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D38">
-        <v>443</v>
+        <v>12</v>
       </c>
       <c r="E38">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F38">
-        <v>443</v>
+        <v>12</v>
       </c>
       <c r="G38">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>443</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
@@ -1588,28 +1588,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D39">
-        <v>129</v>
+        <v>38</v>
       </c>
       <c r="E39">
         <v>3</v>
       </c>
       <c r="F39">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="G39">
         <v>3</v>
       </c>
       <c r="H39">
-        <v>125</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40">
@@ -1620,28 +1620,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D40">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="E40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="G40">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H40">
-        <v>95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D41">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F41">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="G41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H41">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -1689,23 +1689,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D42">
-        <v>12</v>
+        <v>449</v>
       </c>
       <c r="E42">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F42">
-        <v>12</v>
+        <v>403</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="H42">
-        <v>12</v>
+        <v>415</v>
       </c>
     </row>
     <row r="43">
@@ -1721,23 +1721,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D43">
-        <v>295</v>
+        <v>458</v>
       </c>
       <c r="E43">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F43">
-        <v>279</v>
+        <v>444</v>
       </c>
       <c r="G43">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H43">
-        <v>279</v>
+        <v>444</v>
       </c>
     </row>
     <row r="44">
@@ -1753,23 +1753,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D44">
-        <v>248</v>
+        <v>129</v>
       </c>
       <c r="E44">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>194</v>
+        <v>125</v>
       </c>
       <c r="G44">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H44">
-        <v>194</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45">
@@ -1785,23 +1785,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D45">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="E45">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F45">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="G45">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H45">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46">
@@ -1817,23 +1817,23 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D46">
-        <v>691</v>
+        <v>61</v>
       </c>
       <c r="E46">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F46">
-        <v>691</v>
+        <v>61</v>
       </c>
       <c r="G46">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>691</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47">
@@ -1849,23 +1849,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D47">
-        <v>684</v>
+        <v>30</v>
       </c>
       <c r="E47">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="G47">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="H47">
-        <v>159</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48">
@@ -1881,23 +1881,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D48">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="E48">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F48">
-        <v>193</v>
+        <v>263</v>
       </c>
       <c r="G48">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H48">
-        <v>207</v>
+        <v>263</v>
       </c>
     </row>
     <row r="49">
@@ -1913,23 +1913,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D49">
-        <v>724</v>
+        <v>258</v>
       </c>
       <c r="E49">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F49">
-        <v>708</v>
+        <v>204</v>
       </c>
       <c r="G49">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H49">
-        <v>708</v>
+        <v>204</v>
       </c>
     </row>
     <row r="50">
@@ -1945,23 +1945,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D50">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="E50">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F50">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="G50">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H50">
-        <v>12</v>
+        <v>139</v>
       </c>
     </row>
     <row r="51">
@@ -1977,23 +1977,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D51">
-        <v>62</v>
+        <v>681</v>
       </c>
       <c r="E51">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F51">
-        <v>62</v>
+        <v>681</v>
       </c>
       <c r="G51">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="H51">
-        <v>62</v>
+        <v>681</v>
       </c>
     </row>
     <row r="52">
@@ -2009,23 +2009,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D52">
-        <v>12</v>
+        <v>708</v>
       </c>
       <c r="E52">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F52">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="H52">
-        <v>12</v>
+        <v>164</v>
       </c>
     </row>
     <row r="53">
@@ -2041,23 +2041,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D53">
-        <v>714</v>
+        <v>291</v>
       </c>
       <c r="E53">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="F53">
-        <v>682</v>
+        <v>193</v>
       </c>
       <c r="G53">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H53">
-        <v>682</v>
+        <v>207</v>
       </c>
     </row>
     <row r="54">
@@ -2073,23 +2073,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D54">
-        <v>665</v>
+        <v>704</v>
       </c>
       <c r="E54">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="F54">
-        <v>665</v>
+        <v>688</v>
       </c>
       <c r="G54">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H54">
-        <v>665</v>
+        <v>688</v>
       </c>
     </row>
     <row r="55">
@@ -2105,23 +2105,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D55">
-        <v>1503</v>
+        <v>32</v>
       </c>
       <c r="E55">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="F55">
-        <v>1257</v>
+        <v>14</v>
       </c>
       <c r="G55">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="H55">
-        <v>1257</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
@@ -2137,23 +2137,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D56">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="G56">
         <v>1</v>
       </c>
       <c r="H56">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="57">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D57">
-        <v>14</v>
+        <v>364</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="G57">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58">
@@ -2201,23 +2201,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D58">
-        <v>1667</v>
+        <v>724</v>
       </c>
       <c r="E58">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="F58">
-        <v>1158</v>
+        <v>692</v>
       </c>
       <c r="G58">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="H58">
-        <v>1188</v>
+        <v>692</v>
       </c>
     </row>
     <row r="59">
@@ -2233,23 +2233,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D59">
-        <v>34</v>
+        <v>584</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="F59">
-        <v>10</v>
+        <v>584</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H59">
-        <v>10</v>
+        <v>584</v>
       </c>
     </row>
     <row r="60">
@@ -2265,23 +2265,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D60">
-        <v>86</v>
+        <v>1473</v>
       </c>
       <c r="E60">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="F60">
-        <v>84</v>
+        <v>1194</v>
       </c>
       <c r="G60">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="H60">
-        <v>84</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="61">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D61">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="E61">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F61">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="G61">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H61">
-        <v>104</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62">
@@ -2329,215 +2329,215 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D62">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F62">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D63">
-        <v>86</v>
+        <v>1736</v>
       </c>
       <c r="E63">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>1207</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D64">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D65">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>186</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D67">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D68">
+        <v>24</v>
+      </c>
+      <c r="E68">
         <v>1</v>
       </c>
-      <c r="E68">
-        <v>0</v>
-      </c>
       <c r="F68">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="69">
@@ -2548,16 +2548,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D69">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2580,16 +2580,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2612,16 +2612,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2644,16 +2644,16 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D72">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -2681,11 +2681,11 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D73">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -2713,11 +2713,11 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -2745,11 +2745,11 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D75">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2777,11 +2777,11 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -2809,11 +2809,11 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2841,11 +2841,11 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D78">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2868,16 +2868,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2900,16 +2900,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D80">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2932,16 +2932,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2964,16 +2964,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D82">
-        <v>921</v>
+        <v>3</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2996,16 +2996,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3028,16 +3028,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D84">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3065,11 +3065,11 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D85">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3097,11 +3097,11 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D86">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3129,11 +3129,11 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3161,11 +3161,11 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3193,11 +3193,11 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D89">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3225,11 +3225,11 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3257,11 +3257,11 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D91">
-        <v>302</v>
+        <v>38</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D92">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D93">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3348,16 +3348,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D94">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3380,16 +3380,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D95">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3412,16 +3412,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3444,16 +3444,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3476,16 +3476,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D98">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3513,11 +3513,11 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3545,11 +3545,11 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D100">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3577,11 +3577,11 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D101">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3609,11 +3609,11 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D102">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3641,11 +3641,11 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D103">
-        <v>10</v>
+        <v>51</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3673,11 +3673,11 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D104">
-        <v>253</v>
+        <v>1</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3705,11 +3705,11 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D105">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D107">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3833,11 +3833,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D109">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D110">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D111">
-        <v>324</v>
+        <v>1</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D112">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D113">
-        <v>134</v>
+        <v>1</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3988,16 +3988,16 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>269</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4020,16 +4020,16 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D115">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4052,16 +4052,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4084,16 +4084,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D117">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4116,16 +4116,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D118">
-        <v>2</v>
+        <v>98</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D119">
@@ -4185,11 +4185,11 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4217,11 +4217,11 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D121">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4244,16 +4244,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jinko 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D122">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4276,16 +4276,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D123">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4308,12 +4308,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D124">
@@ -4340,16 +4340,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D125">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D126">
@@ -4404,16 +4404,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 625</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D127">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4441,11 +4441,11 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4473,11 +4473,11 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D129">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4500,16 +4500,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D130">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4532,12 +4532,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D131">
@@ -4564,16 +4564,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4596,16 +4596,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4628,16 +4628,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D134">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4660,16 +4660,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4692,16 +4692,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D136">
-        <v>89</v>
+        <v>3</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4724,16 +4724,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D137">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4756,16 +4756,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D138">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4793,11 +4793,11 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D139">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4825,11 +4825,11 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D140">
-        <v>359</v>
+        <v>1</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4857,11 +4857,11 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D141">
-        <v>391</v>
+        <v>89</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4889,11 +4889,11 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D142">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4921,11 +4921,11 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D143">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4953,11 +4953,11 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D144">
-        <v>123</v>
+        <v>32</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4985,11 +4985,11 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D145">
-        <v>50</v>
+        <v>326</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5017,11 +5017,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D146">
-        <v>206</v>
+        <v>381</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5049,7 +5049,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D147">
@@ -5081,11 +5081,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D148">
-        <v>1</v>
+        <v>123</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D149">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D150">
-        <v>158</v>
+        <v>24</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5177,11 +5177,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D151">
-        <v>248</v>
+        <v>1</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D152">
-        <v>303</v>
+        <v>1</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5241,11 +5241,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D153">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D154">
-        <v>744</v>
+        <v>194</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D155">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5337,11 +5337,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D156">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D157">
-        <v>348</v>
+        <v>2</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D158">
-        <v>12</v>
+        <v>299</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D159">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5465,11 +5465,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D160">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D161">
-        <v>582</v>
+        <v>348</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D162">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D163">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D164">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5620,16 +5620,16 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>432</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5647,21 +5647,21 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D166">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5679,21 +5679,21 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D167">
-        <v>56</v>
+        <v>19</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5711,21 +5711,21 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D168">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5743,21 +5743,21 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D169">
-        <v>4</v>
+        <v>432</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5775,21 +5775,21 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D170">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -5821,7 +5821,7 @@
         </is>
       </c>
       <c r="D171">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="D172">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5871,21 +5871,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D173">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5903,21 +5903,21 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5935,21 +5935,21 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5967,21 +5967,21 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Jinko 535</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D176">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5999,21 +5999,21 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D177">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="D178">
-        <v>5005</v>
+        <v>1</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -6077,7 +6077,7 @@
         </is>
       </c>
       <c r="D179">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6095,21 +6095,21 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D180">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6127,21 +6127,21 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Jinko 535</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D181">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6159,21 +6159,21 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D182">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6191,21 +6191,21 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Jinko 545</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D183">
-        <v>3</v>
+        <v>4789</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6223,21 +6223,21 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D184">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6269,7 +6269,7 @@
         </is>
       </c>
       <c r="D185">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6292,7 +6292,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -6301,7 +6301,7 @@
         </is>
       </c>
       <c r="D186">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="D187">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6351,21 +6351,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Jinko 545</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D188">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6383,21 +6383,21 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D189">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6415,21 +6415,21 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D190">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6447,21 +6447,21 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D191">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6479,17 +6479,17 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D192">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6525,7 +6525,7 @@
         </is>
       </c>
       <c r="D193">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6548,16 +6548,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D194">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6580,16 +6580,16 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D195">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6612,16 +6612,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6644,16 +6644,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D197">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6676,16 +6676,16 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D198">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6708,16 +6708,16 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D199">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6740,16 +6740,16 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D200">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -6772,16 +6772,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D201">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6804,16 +6804,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D202">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6841,11 +6841,11 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D203">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6873,11 +6873,11 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D204">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6905,11 +6905,11 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D205">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6937,11 +6937,11 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D206">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6969,11 +6969,11 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -7001,11 +7001,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D208">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7033,11 +7033,11 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D209">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7065,11 +7065,11 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D210">
-        <v>290</v>
+        <v>21</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7097,11 +7097,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D211">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D212">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D213">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D214">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D215">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D216">
-        <v>385</v>
+        <v>2</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D217">
-        <v>29</v>
+        <v>301</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D218">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7348,16 +7348,16 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D219">
-        <v>352</v>
+        <v>10</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7380,16 +7380,16 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D220">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7412,16 +7412,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D221">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7444,16 +7444,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D222">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7476,16 +7476,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D223">
-        <v>25</v>
+        <v>476</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7508,16 +7508,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D224">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7540,16 +7540,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D225">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7577,11 +7577,11 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D226">
-        <v>7</v>
+        <v>194</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7609,11 +7609,11 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D227">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7641,11 +7641,11 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D228">
-        <v>488</v>
+        <v>51</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7673,11 +7673,11 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D229">
-        <v>186</v>
+        <v>24</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7705,11 +7705,11 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D230">
-        <v>287</v>
+        <v>25</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7737,11 +7737,11 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D231">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7769,11 +7769,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D232">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D233">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7833,11 +7833,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D234">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7865,11 +7865,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D235">
-        <v>101</v>
+        <v>488</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D236">
-        <v>48</v>
+        <v>160</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D237">
-        <v>393</v>
+        <v>287</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D238">
-        <v>6</v>
+        <v>339</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D239">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D240">
-        <v>541</v>
+        <v>23</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D241">
-        <v>186</v>
+        <v>43</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D242">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D243">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D244">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D245">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D246">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8244,16 +8244,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>565</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8276,16 +8276,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>186</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8308,16 +8308,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D249">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8340,16 +8340,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D250">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8372,16 +8372,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D251">
-        <v>7</v>
+        <v>349</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8404,16 +8404,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D252">
-        <v>2</v>
+        <v>74</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8436,16 +8436,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D254">
@@ -8500,12 +8500,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D255">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D256">
@@ -8564,16 +8564,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D257">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -8596,16 +8596,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D258">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8628,16 +8628,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -8660,16 +8660,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D260">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -8692,16 +8692,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D261">
-        <v>494</v>
+        <v>1</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -8724,16 +8724,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D262">
-        <v>166</v>
+        <v>2</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -8756,16 +8756,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D263">
-        <v>146</v>
+        <v>1</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -8788,16 +8788,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D264">
-        <v>746</v>
+        <v>4</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -8820,16 +8820,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D265">
-        <v>95</v>
+        <v>1</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -8852,16 +8852,16 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D266">
-        <v>226</v>
+        <v>24</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -8889,11 +8889,11 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D267">
-        <v>206</v>
+        <v>467</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8921,11 +8921,11 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D268">
-        <v>885</v>
+        <v>86</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -8953,11 +8953,11 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D269">
-        <v>1354</v>
+        <v>214</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -8985,11 +8985,11 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D270">
-        <v>146</v>
+        <v>756</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -9017,11 +9017,11 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D271">
-        <v>764</v>
+        <v>111</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -9049,11 +9049,11 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D272">
-        <v>27</v>
+        <v>238</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -9081,11 +9081,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D273">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -9113,11 +9113,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D274">
-        <v>132</v>
+        <v>875</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -9145,11 +9145,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D275">
-        <v>46</v>
+        <v>1432</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -9177,11 +9177,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D276">
-        <v>52</v>
+        <v>143</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -9209,11 +9209,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D277">
-        <v>26</v>
+        <v>764</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -9241,11 +9241,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D278">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -9273,11 +9273,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D279">
-        <v>274</v>
+        <v>187</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -9305,11 +9305,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D280">
-        <v>49</v>
+        <v>128</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -9337,11 +9337,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D281">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -9369,11 +9369,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D282">
-        <v>261</v>
+        <v>52</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D283">
-        <v>586</v>
+        <v>26</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -9433,11 +9433,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D284">
-        <v>180</v>
+        <v>249</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D285">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D286">
-        <v>323</v>
+        <v>188</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -9529,11 +9529,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D287">
-        <v>437</v>
+        <v>19</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -9561,11 +9561,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D288">
-        <v>479</v>
+        <v>286</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -9593,11 +9593,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D289">
-        <v>91</v>
+        <v>586</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -9625,11 +9625,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D290">
-        <v>382</v>
+        <v>200</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -9657,11 +9657,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D291">
-        <v>659</v>
+        <v>178</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -9684,16 +9684,16 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D292">
-        <v>70</v>
+        <v>262</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9716,27 +9716,219 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="D293">
+        <v>474</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+      <c r="G293">
+        <v>0</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="D294">
+        <v>684</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="D295">
+        <v>25</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>0</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="D296">
+        <v>649</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+      <c r="G296">
+        <v>0</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="D297">
+        <v>577</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
+      <c r="G297">
+        <v>0</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
           <t>TCT_Pin khác</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr">
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>DBN</t>
+        </is>
+      </c>
+      <c r="D298">
+        <v>70</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
+      <c r="G298">
+        <v>0</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="D293">
+      <c r="D299">
         <v>2</v>
       </c>
-      <c r="E293">
-        <v>0</v>
-      </c>
-      <c r="F293">
-        <v>0</v>
-      </c>
-      <c r="G293">
-        <v>0</v>
-      </c>
-      <c r="H293">
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
+      </c>
+      <c r="H299">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H299"/>
+  <dimension ref="A1:H305"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -436,28 +436,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -468,16 +468,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -486,10 +486,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
@@ -505,23 +505,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -537,11 +537,11 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -564,28 +564,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D7">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7">
-        <v>67</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -596,28 +596,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -633,23 +633,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D9">
-        <v>243</v>
+        <v>67</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H9">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10">
@@ -665,23 +665,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D11">
-        <v>39</v>
+        <v>243</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H11">
-        <v>39</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -729,23 +729,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D12">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -761,23 +761,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D13">
-        <v>271</v>
+        <v>47</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>111</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
@@ -793,23 +793,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D14">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>16</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -825,23 +825,23 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D15">
-        <v>197</v>
+        <v>271</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F15">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="G15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H15">
-        <v>164</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -857,23 +857,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D16">
-        <v>302</v>
+        <v>16</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F16">
-        <v>242</v>
+        <v>16</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>242</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -889,23 +889,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D17">
-        <v>56</v>
+        <v>423</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F17">
-        <v>24</v>
+        <v>358</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H17">
-        <v>24</v>
+        <v>358</v>
       </c>
     </row>
     <row r="18">
@@ -921,23 +921,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D18">
-        <v>4</v>
+        <v>266</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>4</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19">
@@ -948,28 +948,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D19">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>244</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -980,28 +980,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D20">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>20</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
@@ -1017,23 +1017,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>196</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22">
@@ -1049,23 +1049,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D22">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G22">
         <v>1</v>
       </c>
       <c r="H22">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
@@ -1081,23 +1081,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D23">
-        <v>287</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>239</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H23">
-        <v>239</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1113,23 +1113,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D24">
-        <v>173</v>
+        <v>14</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>109</v>
+        <v>14</v>
       </c>
       <c r="G24">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H24">
-        <v>109</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
@@ -1145,23 +1145,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>247</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F25">
-        <v>13</v>
+        <v>200</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="H25">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D26">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F26">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H26">
-        <v>144</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27">
@@ -1209,23 +1209,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D27">
-        <v>362</v>
+        <v>23</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G27">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H27">
-        <v>163</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D28">
-        <v>92</v>
+        <v>292</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="F28">
-        <v>92</v>
+        <v>256</v>
       </c>
       <c r="G28">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H28">
-        <v>92</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D29">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F29">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="G29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H29">
-        <v>86</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D30">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D32">
-        <v>218</v>
+        <v>90</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H32">
-        <v>34</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D33">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G33">
         <v>2</v>
       </c>
       <c r="H33">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
@@ -1433,23 +1433,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D34">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="E34">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>723</v>
+        <v>10</v>
       </c>
       <c r="G34">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="H34">
-        <v>723</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -1465,23 +1465,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D35">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G35">
         <v>2</v>
       </c>
       <c r="H35">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36">
@@ -1497,23 +1497,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D36">
-        <v>283</v>
+        <v>24</v>
       </c>
       <c r="E36">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F36">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="G36">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>240</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37">
@@ -1529,23 +1529,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D37">
-        <v>333</v>
+        <v>808</v>
       </c>
       <c r="E37">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="F37">
-        <v>227</v>
+        <v>575</v>
       </c>
       <c r="G37">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="H37">
-        <v>227</v>
+        <v>575</v>
       </c>
     </row>
     <row r="38">
@@ -1561,23 +1561,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H38">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39">
@@ -1593,23 +1593,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D39">
-        <v>38</v>
+        <v>247</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F39">
-        <v>38</v>
+        <v>194</v>
       </c>
       <c r="G39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H39">
-        <v>38</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40">
@@ -1620,28 +1620,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D40">
+        <v>48</v>
+      </c>
+      <c r="E40">
         <v>2</v>
       </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
       <c r="F40">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D41">
-        <v>45</v>
+        <v>283</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F41">
-        <v>45</v>
+        <v>201</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H41">
-        <v>45</v>
+        <v>201</v>
       </c>
     </row>
     <row r="42">
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D42">
-        <v>449</v>
+        <v>20</v>
       </c>
       <c r="E42">
+        <v>2</v>
+      </c>
+      <c r="F42">
         <v>20</v>
       </c>
-      <c r="F42">
-        <v>403</v>
-      </c>
       <c r="G42">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="H42">
-        <v>415</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -1716,28 +1716,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D43">
-        <v>458</v>
+        <v>18</v>
       </c>
       <c r="E43">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>444</v>
+        <v>18</v>
       </c>
       <c r="G43">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>444</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -1748,28 +1748,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D44">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H44">
-        <v>125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1780,28 +1780,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D45">
-        <v>146</v>
+        <v>2</v>
       </c>
       <c r="E45">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="G45">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H45">
-        <v>89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1812,28 +1812,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D46">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F46">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="G46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>61</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47">
@@ -1849,23 +1849,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D47">
-        <v>30</v>
+        <v>445</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="F47">
-        <v>30</v>
+        <v>418</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="H47">
-        <v>30</v>
+        <v>418</v>
       </c>
     </row>
     <row r="48">
@@ -1881,23 +1881,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D48">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E48">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F48">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G48">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H48">
-        <v>263</v>
+        <v>268</v>
       </c>
     </row>
     <row r="49">
@@ -1913,23 +1913,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D49">
-        <v>258</v>
+        <v>157</v>
       </c>
       <c r="E49">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="G49">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H49">
-        <v>204</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50">
@@ -1945,23 +1945,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D50">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E50">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F50">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="G50">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H50">
-        <v>139</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51">
@@ -1977,23 +1977,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D51">
-        <v>681</v>
+        <v>18</v>
       </c>
       <c r="E51">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <v>681</v>
+        <v>0</v>
       </c>
       <c r="G51">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H51">
-        <v>681</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2009,23 +2009,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D52">
-        <v>708</v>
+        <v>52</v>
       </c>
       <c r="E52">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F52">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="G52">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H52">
-        <v>164</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53">
@@ -2041,23 +2041,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D53">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="E53">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F53">
-        <v>193</v>
+        <v>238</v>
       </c>
       <c r="G53">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H53">
-        <v>207</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54">
@@ -2073,23 +2073,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D54">
-        <v>704</v>
+        <v>261</v>
       </c>
       <c r="E54">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F54">
-        <v>688</v>
+        <v>182</v>
       </c>
       <c r="G54">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="H54">
-        <v>688</v>
+        <v>182</v>
       </c>
     </row>
     <row r="55">
@@ -2105,23 +2105,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D55">
-        <v>32</v>
+        <v>107</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F55">
-        <v>14</v>
+        <v>107</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H55">
-        <v>14</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56">
@@ -2137,23 +2137,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D56">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H56">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D57">
-        <v>364</v>
+        <v>664</v>
       </c>
       <c r="E57">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F57">
-        <v>340</v>
+        <v>504</v>
       </c>
       <c r="G57">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H57">
-        <v>340</v>
+        <v>504</v>
       </c>
     </row>
     <row r="58">
@@ -2201,23 +2201,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D58">
-        <v>724</v>
+        <v>708</v>
       </c>
       <c r="E58">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="F58">
-        <v>692</v>
+        <v>61</v>
       </c>
       <c r="G58">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H58">
-        <v>692</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59">
@@ -2233,23 +2233,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D59">
-        <v>584</v>
+        <v>143</v>
       </c>
       <c r="E59">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F59">
-        <v>584</v>
+        <v>71</v>
       </c>
       <c r="G59">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="H59">
-        <v>584</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60">
@@ -2265,23 +2265,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D60">
-        <v>1473</v>
+        <v>613</v>
       </c>
       <c r="E60">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F60">
-        <v>1194</v>
+        <v>493</v>
       </c>
       <c r="G60">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="H60">
-        <v>1194</v>
+        <v>493</v>
       </c>
     </row>
     <row r="61">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D61">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H61">
-        <v>51</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
@@ -2329,23 +2329,23 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D62">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
@@ -2361,23 +2361,23 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D63">
-        <v>1736</v>
+        <v>30</v>
       </c>
       <c r="E63">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="F63">
-        <v>1207</v>
+        <v>10</v>
       </c>
       <c r="G63">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>1237</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64">
@@ -2393,23 +2393,23 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D64">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="E64">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F64">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="G64">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H64">
-        <v>68</v>
+        <v>151</v>
       </c>
     </row>
     <row r="65">
@@ -2425,23 +2425,23 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D65">
-        <v>76</v>
+        <v>777</v>
       </c>
       <c r="E65">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="F65">
-        <v>74</v>
+        <v>693</v>
       </c>
       <c r="G65">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="H65">
-        <v>74</v>
+        <v>693</v>
       </c>
     </row>
     <row r="66">
@@ -2457,23 +2457,23 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D66">
-        <v>186</v>
+        <v>600</v>
       </c>
       <c r="E66">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F66">
-        <v>180</v>
+        <v>594</v>
       </c>
       <c r="G66">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H66">
-        <v>186</v>
+        <v>594</v>
       </c>
     </row>
     <row r="67">
@@ -2489,23 +2489,23 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D67">
-        <v>58</v>
+        <v>1324</v>
       </c>
       <c r="E67">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="F67">
-        <v>34</v>
+        <v>1061</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="H67">
-        <v>34</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="68">
@@ -2521,75 +2521,75 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D68">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D69">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="G69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D70">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2607,149 +2607,149 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D71">
-        <v>22</v>
+        <v>1446</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>975</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>183</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D73">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H73">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>206</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H74">
-        <v>0</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D75">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2767,33 +2767,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>157</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F76">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77">
@@ -2804,16 +2804,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D78">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2868,16 +2868,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D79">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D80">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2937,11 +2937,11 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D81">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2969,11 +2969,11 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D82">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3001,11 +3001,11 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3033,11 +3033,11 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D84">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3060,16 +3060,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3092,16 +3092,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D86">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3124,16 +3124,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3156,16 +3156,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3188,16 +3188,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D89">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3220,16 +3220,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D90">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3252,16 +3252,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D91">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3353,11 +3353,11 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D94">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3385,11 +3385,11 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3417,11 +3417,11 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D96">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3449,11 +3449,11 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D97">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3481,11 +3481,11 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D98">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3508,16 +3508,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D99">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -3540,16 +3540,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D100">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3572,16 +3572,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3604,16 +3604,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3636,16 +3636,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D103">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3668,16 +3668,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D105">
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D106">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D107">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D108">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3833,11 +3833,11 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D109">
-        <v>247</v>
+        <v>1</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D110">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D111">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D112">
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D114">
-        <v>269</v>
+        <v>29</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4025,11 +4025,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D115">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4057,11 +4057,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D116">
-        <v>400</v>
+        <v>154</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4089,11 +4089,11 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D117">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4121,11 +4121,11 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D118">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4148,16 +4148,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4180,16 +4180,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4212,16 +4212,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>166</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4244,16 +4244,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D122">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -4276,16 +4276,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D123">
-        <v>2</v>
+        <v>220</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4308,16 +4308,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4340,16 +4340,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4377,11 +4377,11 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -4404,16 +4404,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jinko 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D127">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4436,16 +4436,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D128">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4468,16 +4468,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4500,16 +4500,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D130">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4532,16 +4532,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D131">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4573,7 +4573,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4596,16 +4596,16 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D133">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -4628,16 +4628,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 625</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D134">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4660,16 +4660,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D135">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4692,16 +4692,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D136">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4724,16 +4724,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4756,16 +4756,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D138">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4788,16 +4788,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D139">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4820,12 +4820,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D140">
@@ -4852,16 +4852,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D141">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4884,16 +4884,16 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D142">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4916,16 +4916,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D143">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4948,16 +4948,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D144">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4980,16 +4980,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D145">
-        <v>326</v>
+        <v>2</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5017,11 +5017,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D146">
-        <v>381</v>
+        <v>16</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5049,11 +5049,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D147">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D148">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D149">
-        <v>50</v>
+        <v>217</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D150">
-        <v>24</v>
+        <v>3604</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5177,11 +5177,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D152">
-        <v>1</v>
+        <v>259</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5241,11 +5241,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D153">
-        <v>4</v>
+        <v>316</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D154">
-        <v>194</v>
+        <v>109</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D155">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5337,11 +5337,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D156">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>243</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D158">
-        <v>299</v>
+        <v>114</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D159">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5465,11 +5465,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D160">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D161">
-        <v>348</v>
+        <v>226</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D162">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D163">
-        <v>32</v>
+        <v>131</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D164">
-        <v>3</v>
+        <v>198</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5625,11 +5625,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D165">
-        <v>432</v>
+        <v>185</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5657,11 +5657,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D166">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D167">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5721,11 +5721,11 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D168">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -5753,11 +5753,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D169">
-        <v>432</v>
+        <v>76</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5780,16 +5780,16 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>95</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5807,21 +5807,21 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D171">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5839,21 +5839,21 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D172">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5871,21 +5871,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D173">
-        <v>4</v>
+        <v>320</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5903,21 +5903,21 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D174">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5935,21 +5935,21 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D175">
-        <v>6</v>
+        <v>616</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5967,7 +5967,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5977,11 +5977,11 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D176">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5999,7 +5999,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6009,11 +6009,11 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D177">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6031,7 +6031,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6041,11 +6041,11 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D178">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6063,7 +6063,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6073,11 +6073,11 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6095,7 +6095,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6105,11 +6105,11 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6127,21 +6127,21 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jinko 535</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D181">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6159,21 +6159,21 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D182">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6191,7 +6191,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6201,11 +6201,11 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D183">
-        <v>4789</v>
+        <v>1122</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6223,7 +6223,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6233,11 +6233,11 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D184">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6255,7 +6255,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6265,11 +6265,11 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D185">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6287,7 +6287,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6297,11 +6297,11 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D186">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6319,7 +6319,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6329,11 +6329,11 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D187">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -6351,17 +6351,17 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Jinko 545</t>
+          <t>Jinko 535</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D188">
@@ -6383,7 +6383,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6393,11 +6393,11 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6415,21 +6415,21 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D190">
-        <v>5</v>
+        <v>4285</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6447,21 +6447,21 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D191">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="D192">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6511,21 +6511,21 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D193">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6543,21 +6543,21 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D194">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6575,21 +6575,21 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Jinko 545</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D195">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6607,21 +6607,21 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D196">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -6639,21 +6639,21 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D197">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6671,21 +6671,21 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D198">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6703,21 +6703,21 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D199">
-        <v>1</v>
+        <v>540</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6735,17 +6735,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>TTQH</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D200">
@@ -6772,16 +6772,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D201">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6804,16 +6804,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D202">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6836,16 +6836,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D203">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6868,16 +6868,16 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D204">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="D205">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6932,16 +6932,16 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D206">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6964,16 +6964,16 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D207">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -6996,16 +6996,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D208">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7028,16 +7028,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D209">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7060,16 +7060,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D210">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7097,11 +7097,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D211">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D212">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D213">
-        <v>8</v>
+        <v>99</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D214">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D215">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D216">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D217">
-        <v>301</v>
+        <v>4</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D218">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D219">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D220">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7417,11 +7417,11 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7449,11 +7449,11 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D222">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7481,11 +7481,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D223">
-        <v>476</v>
+        <v>2</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7513,11 +7513,11 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D224">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7545,11 +7545,11 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D225">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D226">
-        <v>194</v>
+        <v>10</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7604,16 +7604,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D227">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7636,16 +7636,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D228">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7668,16 +7668,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D229">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7700,16 +7700,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D230">
-        <v>25</v>
+        <v>543</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7732,16 +7732,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D231">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7769,11 +7769,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D232">
-        <v>166</v>
+        <v>300</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D233">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7833,11 +7833,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D234">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7865,11 +7865,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D235">
-        <v>488</v>
+        <v>24</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D236">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D237">
-        <v>287</v>
+        <v>86</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D238">
-        <v>339</v>
+        <v>150</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D239">
-        <v>118</v>
+        <v>7</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D240">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D241">
-        <v>43</v>
+        <v>290</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D242">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D243">
-        <v>24</v>
+        <v>231</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D244">
-        <v>373</v>
+        <v>197</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D245">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D246">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8249,11 +8249,11 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D247">
-        <v>565</v>
+        <v>43</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8281,11 +8281,11 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D248">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8313,11 +8313,11 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D249">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8345,11 +8345,11 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D250">
-        <v>112</v>
+        <v>450</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8377,11 +8377,11 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D251">
-        <v>349</v>
+        <v>27</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8409,11 +8409,11 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D252">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8441,11 +8441,11 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D253">
-        <v>44</v>
+        <v>461</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8468,16 +8468,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>220</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8500,16 +8500,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8532,16 +8532,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D256">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8564,16 +8564,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D257">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -8596,16 +8596,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D258">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8628,16 +8628,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D259">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -8660,12 +8660,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D260">
@@ -8692,12 +8692,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D261">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D262">
@@ -8756,16 +8756,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D263">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -8788,16 +8788,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D264">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -8820,16 +8820,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -8852,16 +8852,16 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D266">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -8884,16 +8884,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D267">
-        <v>467</v>
+        <v>1</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8916,16 +8916,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D268">
-        <v>86</v>
+        <v>2</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -8948,16 +8948,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D269">
-        <v>214</v>
+        <v>1</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -8980,16 +8980,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D270">
-        <v>756</v>
+        <v>4</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -9012,16 +9012,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D271">
-        <v>111</v>
+        <v>1</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -9044,16 +9044,16 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D272">
-        <v>238</v>
+        <v>24</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -9081,11 +9081,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D273">
-        <v>196</v>
+        <v>486</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -9113,11 +9113,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D274">
-        <v>875</v>
+        <v>260</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -9145,11 +9145,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D275">
-        <v>1432</v>
+        <v>241</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -9177,11 +9177,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D276">
-        <v>143</v>
+        <v>739</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -9209,11 +9209,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D277">
-        <v>764</v>
+        <v>75</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -9241,11 +9241,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D278">
-        <v>59</v>
+        <v>260</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -9273,11 +9273,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D279">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -9305,11 +9305,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D280">
-        <v>128</v>
+        <v>798</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -9337,11 +9337,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D281">
-        <v>14</v>
+        <v>1443</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -9369,11 +9369,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D282">
-        <v>52</v>
+        <v>156</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D283">
-        <v>26</v>
+        <v>569</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -9433,11 +9433,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D284">
-        <v>249</v>
+        <v>184</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D285">
-        <v>19</v>
+        <v>290</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D286">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -9529,11 +9529,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D287">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -9561,11 +9561,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D288">
-        <v>286</v>
+        <v>4</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -9593,11 +9593,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D289">
-        <v>586</v>
+        <v>8</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -9625,11 +9625,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D290">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -9657,11 +9657,11 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D291">
-        <v>178</v>
+        <v>19</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -9689,11 +9689,11 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D292">
-        <v>262</v>
+        <v>435</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9721,11 +9721,11 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D293">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -9753,11 +9753,11 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D294">
-        <v>684</v>
+        <v>170</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -9785,11 +9785,11 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D295">
-        <v>25</v>
+        <v>357</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -9817,11 +9817,11 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D296">
-        <v>649</v>
+        <v>364</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -9849,11 +9849,11 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D297">
-        <v>577</v>
+        <v>168</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -9876,16 +9876,16 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D298">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="E298">
         <v>0</v>
@@ -9908,27 +9908,219 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>TNH</t>
+        </is>
+      </c>
+      <c r="D299">
+        <v>261</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>TNN</t>
+        </is>
+      </c>
+      <c r="D300">
+        <v>604</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>0</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>TQG</t>
+        </is>
+      </c>
+      <c r="D301">
+        <v>64</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>0</v>
+      </c>
+      <c r="G301">
+        <v>0</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>TTH</t>
+        </is>
+      </c>
+      <c r="D302">
+        <v>555</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>0</v>
+      </c>
+      <c r="G302">
+        <v>0</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Longi 620</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>VLG</t>
+        </is>
+      </c>
+      <c r="D303">
+        <v>714</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
           <t>TCT_Pin khác</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>DBN</t>
+        </is>
+      </c>
+      <c r="D304">
+        <v>70</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>0</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>TTQH</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>TCT_Pin khác</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
         <is>
           <t>QNH</t>
         </is>
       </c>
-      <c r="D299">
+      <c r="D305">
         <v>2</v>
       </c>
-      <c r="E299">
-        <v>0</v>
-      </c>
-      <c r="F299">
-        <v>0</v>
-      </c>
-      <c r="G299">
-        <v>0</v>
-      </c>
-      <c r="H299">
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+      <c r="G305">
+        <v>0</v>
+      </c>
+      <c r="H305">
         <v>0</v>
       </c>
     </row>

--- a/data/ton_wms_bc.xlsx
+++ b/data/ton_wms_bc.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H305"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -404,16 +404,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -422,10 +422,10 @@
         <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -436,28 +436,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G3">
         <v>1</v>
       </c>
       <c r="H3">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -468,16 +468,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -486,10 +486,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -500,7 +500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -532,7 +532,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>187</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -550,10 +550,10 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -564,28 +564,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -596,16 +596,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D8">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -633,23 +633,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D9">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>67</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -665,23 +665,23 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D10">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10">
-        <v>16</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -697,23 +697,23 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D11">
-        <v>243</v>
+        <v>16</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G11">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -729,23 +729,23 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D12">
-        <v>51</v>
+        <v>186</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>51</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -761,23 +761,23 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D13">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>8</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14">
@@ -793,23 +793,23 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -820,28 +820,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D15">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="E15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F15">
-        <v>111</v>
+        <v>168</v>
       </c>
       <c r="G15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H15">
-        <v>111</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16">
@@ -852,28 +852,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D16">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
       </c>
       <c r="H16">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -884,28 +884,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D17">
-        <v>423</v>
+        <v>14</v>
       </c>
       <c r="E17">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>358</v>
+        <v>14</v>
       </c>
       <c r="G17">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>358</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
@@ -916,28 +916,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D18">
-        <v>266</v>
+        <v>178</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18">
-        <v>173</v>
+        <v>28</v>
       </c>
       <c r="G18">
         <v>3</v>
       </c>
       <c r="H18">
-        <v>173</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -948,28 +948,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D19">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -980,28 +980,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>170</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>130</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>4</v>
+        <v>130</v>
       </c>
     </row>
     <row r="21">
@@ -1017,23 +1017,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D21">
-        <v>196</v>
+        <v>15</v>
       </c>
       <c r="E21">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>196</v>
+        <v>4</v>
       </c>
       <c r="G21">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>196</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -1049,23 +1049,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D22">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F22">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="G22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22">
-        <v>16</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23">
@@ -1081,23 +1081,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>86</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24">
@@ -1113,23 +1113,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D24">
-        <v>14</v>
+        <v>109</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F24">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H24">
-        <v>14</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
@@ -1145,23 +1145,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D25">
-        <v>247</v>
+        <v>121</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F25">
-        <v>200</v>
+        <v>29</v>
       </c>
       <c r="G25">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H25">
-        <v>200</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26">
@@ -1177,23 +1177,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D26">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26">
-        <v>66</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
@@ -1209,23 +1209,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D27">
-        <v>23</v>
+        <v>616</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F27">
-        <v>23</v>
+        <v>349</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H27">
-        <v>23</v>
+        <v>361</v>
       </c>
     </row>
     <row r="28">
@@ -1241,23 +1241,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D28">
-        <v>292</v>
+        <v>33</v>
       </c>
       <c r="E28">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>256</v>
+        <v>18</v>
       </c>
       <c r="G28">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="H28">
-        <v>256</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -1273,23 +1273,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D29">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F29">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29">
-        <v>64</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30">
@@ -1305,23 +1305,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D30">
-        <v>122</v>
+        <v>38</v>
       </c>
       <c r="E30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="G30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30">
-        <v>122</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1337,23 +1337,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <v>1</v>
       </c>
       <c r="H31">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -1369,23 +1369,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D32">
-        <v>90</v>
+        <v>303</v>
       </c>
       <c r="E32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F32">
-        <v>76</v>
+        <v>191</v>
       </c>
       <c r="G32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H32">
-        <v>76</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33">
@@ -1401,23 +1401,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D33">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -1428,28 +1428,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1460,28 +1460,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D35">
-        <v>135</v>
+        <v>278</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="F35">
-        <v>24</v>
+        <v>258</v>
       </c>
       <c r="G35">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H35">
-        <v>24</v>
+        <v>258</v>
       </c>
     </row>
     <row r="36">
@@ -1492,28 +1492,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D36">
-        <v>24</v>
+        <v>203</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="F36">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H36">
-        <v>24</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37">
@@ -1524,28 +1524,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D37">
-        <v>808</v>
+        <v>117</v>
       </c>
       <c r="E37">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="G37">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H37">
-        <v>575</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1556,28 +1556,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D38">
-        <v>32</v>
+        <v>199</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="F38">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="H38">
-        <v>32</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39">
@@ -1588,28 +1588,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D39">
-        <v>247</v>
+        <v>21</v>
       </c>
       <c r="E39">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="G39">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H39">
-        <v>194</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40">
@@ -1620,28 +1620,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D40">
+        <v>50</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
         <v>48</v>
       </c>
-      <c r="E40">
-        <v>2</v>
-      </c>
-      <c r="F40">
-        <v>30</v>
-      </c>
       <c r="G40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40">
-        <v>30</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41">
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D41">
-        <v>283</v>
+        <v>182</v>
       </c>
       <c r="E41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F41">
-        <v>201</v>
+        <v>117</v>
       </c>
       <c r="G41">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H41">
-        <v>201</v>
+        <v>117</v>
       </c>
     </row>
     <row r="42">
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D42">
-        <v>20</v>
+        <v>459</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F42">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H42">
-        <v>20</v>
+        <v>429</v>
       </c>
     </row>
     <row r="43">
@@ -1716,28 +1716,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D43">
-        <v>18</v>
+        <v>112</v>
       </c>
       <c r="E43">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F43">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H43">
-        <v>18</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44">
@@ -1748,28 +1748,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>532</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45">
@@ -1780,28 +1780,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>898</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>294</v>
       </c>
     </row>
     <row r="46">
@@ -1812,28 +1812,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D46">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E46">
         <v>1</v>
       </c>
       <c r="F46">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="G46">
         <v>1</v>
       </c>
       <c r="H46">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -1849,23 +1849,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D47">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="E47">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F47">
-        <v>418</v>
+        <v>254</v>
       </c>
       <c r="G47">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H47">
-        <v>418</v>
+        <v>254</v>
       </c>
     </row>
     <row r="48">
@@ -1881,23 +1881,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D48">
-        <v>308</v>
+        <v>22</v>
       </c>
       <c r="E48">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="F48">
-        <v>268</v>
+        <v>22</v>
       </c>
       <c r="G48">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>268</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -1913,23 +1913,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D49">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="G49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H49">
-        <v>54</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50">
@@ -1945,23 +1945,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D50">
-        <v>143</v>
+        <v>36</v>
       </c>
       <c r="E50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="G50">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H50">
-        <v>86</v>
+        <v>36</v>
       </c>
     </row>
     <row r="51">
@@ -1977,23 +1977,23 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D51">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52">
@@ -2009,23 +2009,23 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D52">
-        <v>52</v>
+        <v>233</v>
       </c>
       <c r="E52">
         <v>4</v>
       </c>
       <c r="F52">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="G52">
         <v>4</v>
       </c>
       <c r="H52">
-        <v>50</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53">
@@ -2041,23 +2041,23 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D53">
-        <v>263</v>
+        <v>717</v>
       </c>
       <c r="E53">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F53">
-        <v>238</v>
+        <v>553</v>
       </c>
       <c r="G53">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H53">
-        <v>238</v>
+        <v>553</v>
       </c>
     </row>
     <row r="54">
@@ -2073,23 +2073,23 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D54">
-        <v>261</v>
+        <v>592</v>
       </c>
       <c r="E54">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F54">
-        <v>182</v>
+        <v>431</v>
       </c>
       <c r="G54">
         <v>12</v>
       </c>
       <c r="H54">
-        <v>182</v>
+        <v>447</v>
       </c>
     </row>
     <row r="55">
@@ -2105,23 +2105,23 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D55">
-        <v>107</v>
+        <v>1265</v>
       </c>
       <c r="E55">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="F55">
-        <v>107</v>
+        <v>939</v>
       </c>
       <c r="G55">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="H55">
-        <v>107</v>
+        <v>939</v>
       </c>
     </row>
     <row r="56">
@@ -2137,23 +2137,23 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D56">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E56">
         <v>2</v>
       </c>
       <c r="F56">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G56">
         <v>2</v>
       </c>
       <c r="H56">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D57">
-        <v>664</v>
+        <v>49</v>
       </c>
       <c r="E57">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F57">
-        <v>504</v>
+        <v>41</v>
       </c>
       <c r="G57">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H57">
-        <v>504</v>
+        <v>41</v>
       </c>
     </row>
     <row r="58">
@@ -2201,23 +2201,23 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D58">
-        <v>708</v>
+        <v>1820</v>
       </c>
       <c r="E58">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="F58">
-        <v>61</v>
+        <v>1215</v>
       </c>
       <c r="G58">
-        <v>12</v>
+        <v>71</v>
       </c>
       <c r="H58">
-        <v>128</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="59">
@@ -2233,23 +2233,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D59">
-        <v>143</v>
+        <v>228</v>
       </c>
       <c r="E59">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F59">
-        <v>71</v>
+        <v>204</v>
       </c>
       <c r="G59">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H59">
-        <v>71</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60">
@@ -2265,23 +2265,23 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D60">
-        <v>613</v>
+        <v>12</v>
       </c>
       <c r="E60">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F60">
-        <v>493</v>
+        <v>0</v>
       </c>
       <c r="G60">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H60">
-        <v>493</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2297,23 +2297,23 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D61">
-        <v>24</v>
+        <v>160</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F61">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="G61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H61">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62">
@@ -2329,203 +2329,203 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D62">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F62">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="G62">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H62">
-        <v>15</v>
+        <v>221</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D63">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D64">
-        <v>320</v>
+        <v>12</v>
       </c>
       <c r="E64">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="G64">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H64">
-        <v>151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D65">
-        <v>777</v>
+        <v>26</v>
       </c>
       <c r="E65">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="F65">
-        <v>693</v>
+        <v>0</v>
       </c>
       <c r="G65">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H65">
-        <v>693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D66">
-        <v>600</v>
+        <v>90</v>
       </c>
       <c r="E66">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>594</v>
+        <v>0</v>
       </c>
       <c r="G66">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H66">
-        <v>594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D67">
-        <v>1324</v>
+        <v>4</v>
       </c>
       <c r="E67">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>1061</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="H67">
-        <v>1061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D68">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2543,53 +2543,53 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D69">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F69">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H69">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D70">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2607,149 +2607,149 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D71">
-        <v>1446</v>
+        <v>1</v>
       </c>
       <c r="E71">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>975</v>
+        <v>0</v>
       </c>
       <c r="G71">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="H71">
-        <v>1005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D72">
-        <v>183</v>
+        <v>31</v>
       </c>
       <c r="E72">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>183</v>
+        <v>0</v>
       </c>
       <c r="G72">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D73">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F73">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H73">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D74">
-        <v>206</v>
+        <v>4</v>
       </c>
       <c r="E74">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F74">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="G74">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="H74">
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D75">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -2767,33 +2767,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CNCT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D76">
-        <v>157</v>
+        <v>3</v>
       </c>
       <c r="E76">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G76">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H76">
-        <v>157</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -2804,16 +2804,16 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D77">
-        <v>70</v>
+        <v>3</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -2836,16 +2836,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D78">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -2868,16 +2868,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="D80">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -2932,16 +2932,16 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -2964,16 +2964,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D82">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -2996,16 +2996,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3037,7 +3037,7 @@
         </is>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3060,16 +3060,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D85">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3092,16 +3092,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D86">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3124,16 +3124,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D87">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3156,16 +3156,16 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D88">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3188,16 +3188,16 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D89">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3220,16 +3220,16 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3252,16 +3252,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D91">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3289,11 +3289,11 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -3321,11 +3321,11 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D93">
-        <v>101</v>
+        <v>34</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -3348,16 +3348,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -3380,16 +3380,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>CBG</t>
         </is>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -3412,16 +3412,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D96">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -3444,16 +3444,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D97">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -3476,16 +3476,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D98">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -3508,12 +3508,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D99">
@@ -3540,16 +3540,16 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -3572,16 +3572,16 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D101">
-        <v>11</v>
+        <v>184</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -3604,16 +3604,16 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -3636,16 +3636,16 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D103">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -3668,16 +3668,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D104">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -3700,16 +3700,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D105">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -3737,11 +3737,11 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D106">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -3769,11 +3769,11 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D107">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -3801,11 +3801,11 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D109">
@@ -3865,11 +3865,11 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D110">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -3897,11 +3897,11 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -3929,11 +3929,11 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D112">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -3961,11 +3961,11 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D113">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -3993,11 +3993,11 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D114">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4025,11 +4025,11 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D115">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4052,16 +4052,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D116">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4084,16 +4084,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D117">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D118">
@@ -4148,16 +4148,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D119">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4180,16 +4180,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4221,7 +4221,7 @@
         </is>
       </c>
       <c r="D121">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -4244,12 +4244,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D122">
@@ -4276,16 +4276,16 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D123">
-        <v>220</v>
+        <v>3</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -4308,16 +4308,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 625</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D124">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -4340,16 +4340,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D125">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D126">
@@ -4404,16 +4404,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D127">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -4436,16 +4436,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -4468,16 +4468,16 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D129">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -4500,16 +4500,16 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -4532,16 +4532,16 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -4564,16 +4564,16 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D133">
@@ -4628,16 +4628,16 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Jinko 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D134">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -4660,16 +4660,16 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D135">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -4692,16 +4692,16 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>88</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -4724,16 +4724,16 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D137">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -4756,16 +4756,16 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D138">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -4788,16 +4788,16 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D139">
-        <v>10</v>
+        <v>2132</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -4820,16 +4820,16 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -4852,16 +4852,16 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D141">
-        <v>8</v>
+        <v>190</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>504</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -4916,16 +4916,16 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D143">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -4948,16 +4948,16 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>1368</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -4980,16 +4980,16 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D145">
-        <v>2</v>
+        <v>149</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5017,11 +5017,11 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D146">
-        <v>16</v>
+        <v>342</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5049,11 +5049,11 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D147">
-        <v>49</v>
+        <v>1127</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5081,11 +5081,11 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CBG</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D148">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D149">
-        <v>217</v>
+        <v>57</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -5145,11 +5145,11 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D150">
-        <v>3604</v>
+        <v>720</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -5177,11 +5177,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D151">
-        <v>42</v>
+        <v>264</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -5209,11 +5209,11 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D152">
-        <v>259</v>
+        <v>426</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -5241,11 +5241,11 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D153">
-        <v>316</v>
+        <v>249</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -5273,11 +5273,11 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D154">
-        <v>109</v>
+        <v>252</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -5305,11 +5305,11 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D155">
-        <v>112</v>
+        <v>1131</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -5337,11 +5337,11 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D156">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -5369,11 +5369,11 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D157">
-        <v>243</v>
+        <v>849</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -5401,11 +5401,11 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D158">
-        <v>114</v>
+        <v>1</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -5433,11 +5433,11 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D159">
-        <v>82</v>
+        <v>323</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -5465,11 +5465,11 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D160">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -5497,11 +5497,11 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>SLA</t>
         </is>
       </c>
       <c r="D161">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -5529,11 +5529,11 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D162">
-        <v>112</v>
+        <v>874</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -5561,11 +5561,11 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D163">
-        <v>131</v>
+        <v>799</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -5593,11 +5593,11 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D164">
-        <v>198</v>
+        <v>1301</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -5625,11 +5625,11 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D165">
-        <v>185</v>
+        <v>460</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -5657,11 +5657,11 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D166">
-        <v>63</v>
+        <v>136</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -5689,11 +5689,11 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D167">
-        <v>7</v>
+        <v>385</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -5716,12 +5716,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D168">
@@ -5743,21 +5743,21 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D169">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -5775,21 +5775,21 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D170">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -5807,21 +5807,21 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SLA</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D171">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -5839,21 +5839,21 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Jinko 570</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -5871,21 +5871,21 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D173">
-        <v>320</v>
+        <v>7</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -5903,7 +5903,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5913,11 +5913,11 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D174">
-        <v>10</v>
+        <v>11094</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -5935,21 +5935,21 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>TQG</t>
+          <t>COV1-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D175">
-        <v>616</v>
+        <v>8</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -5967,21 +5967,21 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D176">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -5999,17 +5999,17 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CNCT</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D177">
@@ -6031,21 +6031,21 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D178">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -6063,21 +6063,21 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Jinko 535</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D179">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -6095,21 +6095,21 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D180">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -6127,21 +6127,21 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Jinko 570</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D181">
-        <v>4</v>
+        <v>2809</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -6159,21 +6159,21 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV2</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV2-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D182">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -6191,21 +6191,21 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D183">
-        <v>1122</v>
+        <v>10</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -6223,21 +6223,21 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>KV1</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>COV1-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D184">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -6255,21 +6255,21 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D185">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -6287,21 +6287,21 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>Jinko 545</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D186">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -6319,17 +6319,17 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D187">
@@ -6351,21 +6351,21 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Jinko 535</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D188">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -6383,21 +6383,21 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D189">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -6415,7 +6415,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6425,11 +6425,11 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D190">
-        <v>4285</v>
+        <v>3672</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -6447,7 +6447,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>KV2</t>
+          <t>KV3</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>COV2-Công ty CP Công trình Viettel</t>
+          <t>COV3-Công ty CP Công trình Viettel</t>
         </is>
       </c>
       <c r="D191">
@@ -6479,21 +6479,21 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D192">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -6511,21 +6511,21 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D193">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -6543,21 +6543,21 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D194">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -6575,21 +6575,21 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Jinko 545</t>
+          <t>CN_Pin khác</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D195">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -6607,17 +6607,17 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D196">
@@ -6639,21 +6639,21 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D197">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -6671,21 +6671,21 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D198">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -6703,21 +6703,21 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D199">
-        <v>540</v>
+        <v>1</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -6735,17 +6735,17 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>KV3</t>
+          <t>TTQH</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>TCT_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>COV3-Công ty CP Công trình Viettel</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D200">
@@ -6772,16 +6772,16 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D201">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -6804,16 +6804,16 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 615</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D202">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -6836,16 +6836,16 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CN_Pin khác</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D203">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -6868,16 +6868,16 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D204">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -6900,7 +6900,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="D205">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -6932,16 +6932,16 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D206">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -6964,16 +6964,16 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D207">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -6996,16 +6996,16 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D208">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -7028,16 +7028,16 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D209">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -7060,16 +7060,16 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>JA 615</t>
+          <t>JA 620</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -7097,11 +7097,11 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D211">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -7129,11 +7129,11 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D212">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -7161,11 +7161,11 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D213">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -7193,11 +7193,11 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D214">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D215">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -7257,11 +7257,11 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D216">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -7289,11 +7289,11 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D217">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -7321,11 +7321,11 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D218">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -7353,11 +7353,11 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D219">
-        <v>22</v>
+        <v>598</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -7385,11 +7385,11 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D220">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -7412,16 +7412,16 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D221">
-        <v>1</v>
+        <v>114</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -7444,16 +7444,16 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D222">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -7476,16 +7476,16 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D223">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -7508,16 +7508,16 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D224">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -7540,16 +7540,16 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D225">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D226">
-        <v>10</v>
+        <v>148</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -7604,16 +7604,16 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D227">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -7636,16 +7636,16 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D228">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -7668,16 +7668,16 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>TNH</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D229">
-        <v>6</v>
+        <v>174</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -7700,16 +7700,16 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D230">
-        <v>543</v>
+        <v>39</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -7732,16 +7732,16 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>JA 620</t>
+          <t>JA 625</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D231">
-        <v>35</v>
+        <v>199</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -7769,11 +7769,11 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D232">
-        <v>300</v>
+        <v>187</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -7801,11 +7801,11 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D233">
-        <v>62</v>
+        <v>17</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -7833,11 +7833,11 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D234">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -7865,11 +7865,11 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D235">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -7897,11 +7897,11 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D236">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -7929,11 +7929,11 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D237">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -7961,11 +7961,11 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D238">
-        <v>150</v>
+        <v>365</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -7993,11 +7993,11 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D239">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -8025,11 +8025,11 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D240">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -8057,11 +8057,11 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D241">
-        <v>290</v>
+        <v>318</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -8089,11 +8089,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D242">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -8121,11 +8121,11 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D243">
-        <v>231</v>
+        <v>39</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -8153,11 +8153,11 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D244">
-        <v>197</v>
+        <v>130</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -8185,11 +8185,11 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D245">
-        <v>54</v>
+        <v>194</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -8217,11 +8217,11 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D246">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -8244,16 +8244,16 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D247">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -8276,16 +8276,16 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D248">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -8308,16 +8308,16 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>HNI</t>
         </is>
       </c>
       <c r="D249">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -8340,16 +8340,16 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D250">
-        <v>450</v>
+        <v>16</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -8372,16 +8372,16 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Jinko 585</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D251">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -8404,16 +8404,16 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>PTO</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D252">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -8436,16 +8436,16 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D253">
-        <v>461</v>
+        <v>1</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -8468,16 +8468,16 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>QNI</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D254">
-        <v>220</v>
+        <v>1</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -8500,16 +8500,16 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 585</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>QTI</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D255">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -8532,16 +8532,16 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D256">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -8564,16 +8564,16 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D257">
-        <v>144</v>
+        <v>4</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -8596,16 +8596,16 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D258">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -8628,16 +8628,16 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>JA 625</t>
+          <t>Longi 615</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>VLG</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D259">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -8660,16 +8660,16 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>AGG</t>
         </is>
       </c>
       <c r="D260">
-        <v>1</v>
+        <v>433</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -8692,16 +8692,16 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>BNH</t>
         </is>
       </c>
       <c r="D261">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -8724,16 +8724,16 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>HNI</t>
+          <t>CMU</t>
         </is>
       </c>
       <c r="D262">
-        <v>2</v>
+        <v>128</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -8756,16 +8756,16 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>CTO</t>
         </is>
       </c>
       <c r="D263">
-        <v>16</v>
+        <v>396</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -8788,16 +8788,16 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Jinko 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>QNH</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D264">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -8820,16 +8820,16 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>DLK</t>
         </is>
       </c>
       <c r="D265">
-        <v>2</v>
+        <v>188</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -8852,16 +8852,16 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>DNG</t>
         </is>
       </c>
       <c r="D266">
-        <v>1</v>
+        <v>180</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -8884,16 +8884,16 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>DNI</t>
         </is>
       </c>
       <c r="D267">
-        <v>1</v>
+        <v>612</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -8916,16 +8916,16 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Longi 585</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>TNN</t>
+          <t>DTP</t>
         </is>
       </c>
       <c r="D268">
-        <v>2</v>
+        <v>1437</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -8948,16 +8948,16 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>GLI</t>
         </is>
       </c>
       <c r="D269">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -8980,16 +8980,16 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="D270">
-        <v>4</v>
+        <v>421</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -9012,16 +9012,16 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>NBH</t>
+          <t>HPG</t>
         </is>
       </c>
       <c r="D271">
-        <v>1</v>
+        <v>467</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -9044,16 +9044,16 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Longi 615</t>
+          <t>Longi 620</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>TTH</t>
+          <t>HTH</t>
         </is>
       </c>
       <c r="D272">
-        <v>24</v>
+        <v>402</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -9081,11 +9081,11 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>AGG</t>
+          <t>HYN</t>
         </is>
       </c>
       <c r="D273">
-        <v>486</v>
+        <v>57</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -9113,11 +9113,11 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>BNH</t>
+          <t>KHA</t>
         </is>
       </c>
       <c r="D274">
-        <v>260</v>
+        <v>76</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -9145,11 +9145,11 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>CMU</t>
+          <t>LCI</t>
         </is>
       </c>
       <c r="D275">
-        <v>241</v>
+        <v>14</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -9177,11 +9177,11 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>CTO</t>
+          <t>LCU</t>
         </is>
       </c>
       <c r="D276">
-        <v>739</v>
+        <v>62</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -9209,11 +9209,11 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>LDG</t>
         </is>
       </c>
       <c r="D277">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -9241,11 +9241,11 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>DLK</t>
+          <t>LSN</t>
         </is>
       </c>
       <c r="D278">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -9273,11 +9273,11 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>DNG</t>
+          <t>NAN</t>
         </is>
       </c>
       <c r="D279">
-        <v>176</v>
+        <v>702</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -9305,11 +9305,11 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DNI</t>
+          <t>NBH</t>
         </is>
       </c>
       <c r="D280">
-        <v>798</v>
+        <v>376</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -9337,11 +9337,11 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>DTP</t>
+          <t>PTO</t>
         </is>
       </c>
       <c r="D281">
-        <v>1443</v>
+        <v>723</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -9369,11 +9369,11 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>GLI</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D282">
-        <v>156</v>
+        <v>839</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>QNI</t>
         </is>
       </c>
       <c r="D283">
-        <v>569</v>
+        <v>165</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -9433,11 +9433,11 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>HPG</t>
+          <t>QTI</t>
         </is>
       </c>
       <c r="D284">
-        <v>184</v>
+        <v>124</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -9465,11 +9465,11 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>HTH</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D285">
-        <v>290</v>
+        <v>337</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -9497,11 +9497,11 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>HYN</t>
+          <t>TNH</t>
         </is>
       </c>
       <c r="D286">
-        <v>60</v>
+        <v>221</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -9529,11 +9529,11 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>KHA</t>
+          <t>TNN</t>
         </is>
       </c>
       <c r="D287">
-        <v>48</v>
+        <v>421</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -9561,11 +9561,11 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>LCI</t>
+          <t>TQG</t>
         </is>
       </c>
       <c r="D288">
-        <v>4</v>
+        <v>158</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -9593,11 +9593,11 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>LCU</t>
+          <t>TTH</t>
         </is>
       </c>
       <c r="D289">
-        <v>8</v>
+        <v>657</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -9625,11 +9625,11 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>LDG</t>
+          <t>VLG</t>
         </is>
       </c>
       <c r="D290">
-        <v>231</v>
+        <v>434</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -9652,16 +9652,16 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>LSN</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="D291">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -9684,16 +9684,16 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Longi 620</t>
+          <t>TCT_Pin khác</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>NAN</t>
+          <t>QNH</t>
         </is>
       </c>
       <c r="D292">
-        <v>435</v>
+        <v>2</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -9705,422 +9705,6 @@
         <v>0</v>
       </c>
       <c r="H292">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="293">
-      <c r="A293" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C293" t="inlineStr">
-        <is>
-          <t>NBH</t>
-        </is>
-      </c>
-      <c r="D293">
-        <v>473</v>
-      </c>
-      <c r="E293">
-        <v>0</v>
-      </c>
-      <c r="F293">
-        <v>0</v>
-      </c>
-      <c r="G293">
-        <v>0</v>
-      </c>
-      <c r="H293">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B294" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C294" t="inlineStr">
-        <is>
-          <t>PTO</t>
-        </is>
-      </c>
-      <c r="D294">
-        <v>170</v>
-      </c>
-      <c r="E294">
-        <v>0</v>
-      </c>
-      <c r="F294">
-        <v>0</v>
-      </c>
-      <c r="G294">
-        <v>0</v>
-      </c>
-      <c r="H294">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B295" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C295" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="D295">
-        <v>357</v>
-      </c>
-      <c r="E295">
-        <v>0</v>
-      </c>
-      <c r="F295">
-        <v>0</v>
-      </c>
-      <c r="G295">
-        <v>0</v>
-      </c>
-      <c r="H295">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="296">
-      <c r="A296" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B296" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C296" t="inlineStr">
-        <is>
-          <t>QNI</t>
-        </is>
-      </c>
-      <c r="D296">
-        <v>364</v>
-      </c>
-      <c r="E296">
-        <v>0</v>
-      </c>
-      <c r="F296">
-        <v>0</v>
-      </c>
-      <c r="G296">
-        <v>0</v>
-      </c>
-      <c r="H296">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="297">
-      <c r="A297" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>QTI</t>
-        </is>
-      </c>
-      <c r="D297">
-        <v>168</v>
-      </c>
-      <c r="E297">
-        <v>0</v>
-      </c>
-      <c r="F297">
-        <v>0</v>
-      </c>
-      <c r="G297">
-        <v>0</v>
-      </c>
-      <c r="H297">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B298" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>THA</t>
-        </is>
-      </c>
-      <c r="D298">
-        <v>200</v>
-      </c>
-      <c r="E298">
-        <v>0</v>
-      </c>
-      <c r="F298">
-        <v>0</v>
-      </c>
-      <c r="G298">
-        <v>0</v>
-      </c>
-      <c r="H298">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B299" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>TNH</t>
-        </is>
-      </c>
-      <c r="D299">
-        <v>261</v>
-      </c>
-      <c r="E299">
-        <v>0</v>
-      </c>
-      <c r="F299">
-        <v>0</v>
-      </c>
-      <c r="G299">
-        <v>0</v>
-      </c>
-      <c r="H299">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr">
-        <is>
-          <t>TNN</t>
-        </is>
-      </c>
-      <c r="D300">
-        <v>604</v>
-      </c>
-      <c r="E300">
-        <v>0</v>
-      </c>
-      <c r="F300">
-        <v>0</v>
-      </c>
-      <c r="G300">
-        <v>0</v>
-      </c>
-      <c r="H300">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr">
-        <is>
-          <t>TQG</t>
-        </is>
-      </c>
-      <c r="D301">
-        <v>64</v>
-      </c>
-      <c r="E301">
-        <v>0</v>
-      </c>
-      <c r="F301">
-        <v>0</v>
-      </c>
-      <c r="G301">
-        <v>0</v>
-      </c>
-      <c r="H301">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B302" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr">
-        <is>
-          <t>TTH</t>
-        </is>
-      </c>
-      <c r="D302">
-        <v>555</v>
-      </c>
-      <c r="E302">
-        <v>0</v>
-      </c>
-      <c r="F302">
-        <v>0</v>
-      </c>
-      <c r="G302">
-        <v>0</v>
-      </c>
-      <c r="H302">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr">
-        <is>
-          <t>Longi 620</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr">
-        <is>
-          <t>VLG</t>
-        </is>
-      </c>
-      <c r="D303">
-        <v>714</v>
-      </c>
-      <c r="E303">
-        <v>0</v>
-      </c>
-      <c r="F303">
-        <v>0</v>
-      </c>
-      <c r="G303">
-        <v>0</v>
-      </c>
-      <c r="H303">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="304">
-      <c r="A304" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B304" t="inlineStr">
-        <is>
-          <t>TCT_Pin khác</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr">
-        <is>
-          <t>DBN</t>
-        </is>
-      </c>
-      <c r="D304">
-        <v>70</v>
-      </c>
-      <c r="E304">
-        <v>0</v>
-      </c>
-      <c r="F304">
-        <v>0</v>
-      </c>
-      <c r="G304">
-        <v>0</v>
-      </c>
-      <c r="H304">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="305">
-      <c r="A305" t="inlineStr">
-        <is>
-          <t>TTQH</t>
-        </is>
-      </c>
-      <c r="B305" t="inlineStr">
-        <is>
-          <t>TCT_Pin khác</t>
-        </is>
-      </c>
-      <c r="C305" t="inlineStr">
-        <is>
-          <t>QNH</t>
-        </is>
-      </c>
-      <c r="D305">
-        <v>2</v>
-      </c>
-      <c r="E305">
-        <v>0</v>
-      </c>
-      <c r="F305">
-        <v>0</v>
-      </c>
-      <c r="G305">
-        <v>0</v>
-      </c>
-      <c r="H305">
         <v>0</v>
       </c>
     </row>
